--- a/output/peer_comparison.xlsx
+++ b/output/peer_comparison.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Power &amp; Utilities" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Private Banks" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Automobiles" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Consumer Finance" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Public Sector Banks" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Oil &amp; Gas" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="FMCG" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Pharmaceuticals" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="IT Services" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Life Insurance" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Steel" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Automobiles" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Consumer Finance" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FMCG" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IT Services" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Life Insurance" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Oil &amp; Gas" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pharmaceuticals" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Power &amp; Utilities" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Private Banks" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Public Sector Banks" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Steel" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -27,7 +27,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -35,13 +35,50 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <b val="1"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F4E78"/>
+        <bgColor rgb="001F4E78"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFD966"/>
+        <bgColor rgb="00FFD966"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+        <bgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+        <bgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC7CE"/>
+        <bgColor rgb="00FFC7CE"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -56,8 +93,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -423,131 +468,158 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y8"/>
+  <dimension ref="A1:Y9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="27" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="17" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="19" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="20" customWidth="1" min="13" max="13"/>
+    <col width="17" customWidth="1" min="14" max="14"/>
+    <col width="26" customWidth="1" min="15" max="15"/>
+    <col width="34" customWidth="1" min="16" max="16"/>
+    <col width="29" customWidth="1" min="17" max="17"/>
+    <col width="35" customWidth="1" min="18" max="18"/>
+    <col width="28" customWidth="1" min="19" max="19"/>
+    <col width="31" customWidth="1" min="20" max="20"/>
+    <col width="26" customWidth="1" min="21" max="21"/>
+    <col width="30" customWidth="1" min="22" max="22"/>
+    <col width="26" customWidth="1" min="23" max="23"/>
+    <col width="31" customWidth="1" min="24" max="24"/>
+    <col width="28" customWidth="1" min="25" max="25"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>peer_group_name</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>company_id</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>is_benchmark</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>year</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>return_on_equity_pct</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>roce_percentage</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>net_profit_margin_pct</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>debt_to_equity</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>free_cash_flow_cr</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>pat_cagr_5yr</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>revenue_cagr_5yr</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>eps_cagr_5yr</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>interest_coverage</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>asset_turnover</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>composite_quality_score</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>return_on_equity_pct_percentile</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>roce_percentage_percentile</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>net_profit_margin_pct_percentile</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>debt_to_equity_percentile</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>free_cash_flow_cr_percentile</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>pat_cagr_5yr_percentile</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>revenue_cagr_5yr_percentile</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>eps_cagr_5yr_percentile</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>interest_coverage_percentile</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>asset_turnover_percentile</t>
         </is>
@@ -556,12 +628,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Power &amp; Utilities</t>
+          <t>BAJAJ-AUTO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ADANIGREEN</t>
+          <t>Bajaj Auto Ltd</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -575,70 +647,78 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>12.81</v>
+        <v>26.61</v>
       </c>
       <c r="F2" t="n">
-        <v>96.5</v>
+        <v>33.5</v>
       </c>
       <c r="G2" t="n">
-        <v>13.67</v>
+        <v>17.18</v>
       </c>
       <c r="H2" t="n">
-        <v>6.6</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>-13347</v>
-      </c>
-      <c r="J2" t="inlineStr"/>
+        <v>6486</v>
+      </c>
+      <c r="J2" t="n">
+        <v>9.359999999999999</v>
+      </c>
       <c r="K2" t="n">
-        <v>34.98</v>
-      </c>
-      <c r="L2" t="inlineStr"/>
+        <v>8.130000000000001</v>
+      </c>
+      <c r="L2" t="n">
+        <v>10.18</v>
+      </c>
       <c r="M2" t="n">
-        <v>1.71</v>
+        <v>174.42</v>
       </c>
       <c r="N2" t="n">
-        <v>0.1</v>
+        <v>1.14</v>
       </c>
       <c r="O2" t="n">
-        <v>59.67</v>
-      </c>
-      <c r="P2" t="n">
-        <v>42.85714285714285</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>100</v>
-      </c>
-      <c r="R2" t="n">
-        <v>42.85714285714285</v>
-      </c>
-      <c r="S2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T2" t="n">
-        <v>14.28571428571428</v>
-      </c>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="n">
-        <v>100</v>
-      </c>
-      <c r="W2" t="inlineStr"/>
-      <c r="X2" t="n">
-        <v>14.28571428571428</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>21.42857142857143</v>
+        <v>75.48</v>
+      </c>
+      <c r="P2" s="2" t="n">
+        <v>85.71428571428571</v>
+      </c>
+      <c r="Q2" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="R2" s="2" t="n">
+        <v>85.71428571428571</v>
+      </c>
+      <c r="S2" s="3" t="n">
+        <v>42.85714285714286</v>
+      </c>
+      <c r="T2" s="2" t="n">
+        <v>85.71428571428571</v>
+      </c>
+      <c r="U2" s="3" t="n">
+        <v>33.33333333333333</v>
+      </c>
+      <c r="V2" s="3" t="n">
+        <v>57.14285714285714</v>
+      </c>
+      <c r="W2" s="3" t="n">
+        <v>33.33333333333333</v>
+      </c>
+      <c r="X2" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="Y2" s="3" t="n">
+        <v>57.14285714285714</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Power &amp; Utilities</t>
+          <t>EICHERMOT</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ADANIPOWER</t>
+          <t>Eicher Motors Ltd</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -652,70 +732,79 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>48.28</v>
+        <v>22.17</v>
       </c>
       <c r="F3" t="n">
-        <v>32.2</v>
+        <v>31.1</v>
       </c>
       <c r="G3" t="n">
-        <v>41.37</v>
+        <v>24.2</v>
       </c>
       <c r="H3" t="n">
-        <v>0.8</v>
+        <v>0.02</v>
       </c>
       <c r="I3" t="n">
-        <v>17651</v>
-      </c>
-      <c r="J3" t="inlineStr"/>
+        <v>890</v>
+      </c>
+      <c r="J3" t="n">
+        <v>12.68</v>
+      </c>
       <c r="K3" t="n">
-        <v>16.09</v>
-      </c>
-      <c r="L3" t="inlineStr"/>
+        <v>11.04</v>
+      </c>
+      <c r="L3" t="n">
+        <v>12.51</v>
+      </c>
       <c r="M3" t="n">
-        <v>8.300000000000001</v>
+        <v>114.71</v>
       </c>
       <c r="N3" t="n">
-        <v>0.55</v>
+        <v>0.72</v>
       </c>
       <c r="O3" t="n">
-        <v>88.79000000000001</v>
-      </c>
-      <c r="P3" t="n">
-        <v>100</v>
-      </c>
-      <c r="Q3" t="n">
+        <v>72.52</v>
+      </c>
+      <c r="P3" s="3" t="n">
+        <v>57.14285714285714</v>
+      </c>
+      <c r="Q3" s="2" t="n">
+        <v>83.33333333333334</v>
+      </c>
+      <c r="R3" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="S3" s="3" t="n">
+        <v>71.42857142857143</v>
+      </c>
+      <c r="T3" s="3" t="n">
+        <v>42.85714285714285</v>
+      </c>
+      <c r="U3" s="3" t="n">
+        <v>66.66666666666666</v>
+      </c>
+      <c r="V3" s="2" t="n">
         <v>85.71428571428571</v>
       </c>
-      <c r="R3" t="n">
-        <v>85.71428571428571</v>
-      </c>
-      <c r="S3" t="n">
-        <v>85.71428571428572</v>
-      </c>
-      <c r="T3" t="n">
-        <v>85.71428571428571</v>
-      </c>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="n">
-        <v>85.71428571428571</v>
-      </c>
-      <c r="W3" t="inlineStr"/>
-      <c r="X3" t="n">
-        <v>85.71428571428571</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>100</v>
+      <c r="W3" s="3" t="n">
+        <v>66.66666666666666</v>
+      </c>
+      <c r="X3" s="3" t="n">
+        <v>71.42857142857143</v>
+      </c>
+      <c r="Y3" s="3" t="n">
+        <v>28.57142857142857</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Power &amp; Utilities</t>
+          <t>HEROMOTOCO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>JSWENERGY</t>
+          <t xml:space="preserve">Hero MotoCorp Ltd
+</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -729,78 +818,79 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>8.279999999999999</v>
+        <v>21.14</v>
       </c>
       <c r="F4" t="n">
-        <v>8.59</v>
+        <v>29.1</v>
       </c>
       <c r="G4" t="n">
-        <v>15.02</v>
+        <v>9.9</v>
       </c>
       <c r="H4" t="n">
-        <v>1.52</v>
+        <v>0.03</v>
       </c>
       <c r="I4" t="n">
-        <v>-1963</v>
+        <v>3095</v>
       </c>
       <c r="J4" t="n">
-        <v>20.32</v>
+        <v>1.54</v>
       </c>
       <c r="K4" t="n">
-        <v>4.68</v>
+        <v>2.15</v>
       </c>
       <c r="L4" t="n">
-        <v>20.11</v>
+        <v>1.69</v>
       </c>
       <c r="M4" t="n">
-        <v>2.85</v>
+        <v>47.27</v>
       </c>
       <c r="N4" t="n">
-        <v>0.2</v>
+        <v>1.44</v>
       </c>
       <c r="O4" t="n">
-        <v>66.79000000000001</v>
-      </c>
-      <c r="P4" t="n">
+        <v>72.03</v>
+      </c>
+      <c r="P4" s="3" t="n">
+        <v>42.85714285714285</v>
+      </c>
+      <c r="Q4" s="3" t="n">
+        <v>66.66666666666666</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>71.42857142857143</v>
+      </c>
+      <c r="S4" s="3" t="n">
+        <v>57.14285714285715</v>
+      </c>
+      <c r="T4" s="3" t="n">
+        <v>57.14285714285714</v>
+      </c>
+      <c r="U4" s="4" t="n">
+        <v>16.66666666666666</v>
+      </c>
+      <c r="V4" s="4" t="n">
         <v>14.28571428571428</v>
       </c>
-      <c r="Q4" t="n">
-        <v>28.57142857142857</v>
-      </c>
-      <c r="R4" t="n">
+      <c r="W4" s="4" t="n">
+        <v>16.66666666666666</v>
+      </c>
+      <c r="X4" s="3" t="n">
         <v>57.14285714285714</v>
       </c>
-      <c r="S4" t="n">
-        <v>28.57142857142857</v>
-      </c>
-      <c r="T4" t="n">
-        <v>28.57142857142857</v>
-      </c>
-      <c r="U4" t="n">
-        <v>100</v>
-      </c>
-      <c r="V4" t="n">
-        <v>28.57142857142857</v>
-      </c>
-      <c r="W4" t="n">
-        <v>100</v>
-      </c>
-      <c r="X4" t="n">
-        <v>28.57142857142857</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>57.14285714285714</v>
+      <c r="Y4" s="2" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Power &amp; Utilities</t>
+          <t>M&amp;M</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>NHPC</t>
+          <t xml:space="preserve">Mahindra &amp; Mahindra Ltd
+</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -814,163 +904,163 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>10.41</v>
+        <v>18.54</v>
       </c>
       <c r="F5" t="n">
-        <v>7.67</v>
+        <v>26.98</v>
       </c>
       <c r="G5" t="n">
-        <v>41.82</v>
+        <v>8.82</v>
       </c>
       <c r="H5" t="n">
-        <v>0.84</v>
+        <v>1.64</v>
       </c>
       <c r="I5" t="n">
-        <v>970</v>
+        <v>-11245</v>
       </c>
       <c r="J5" t="n">
-        <v>7.27</v>
+        <v>15.32</v>
       </c>
       <c r="K5" t="n">
-        <v>1.4</v>
+        <v>5.84</v>
       </c>
       <c r="L5" t="n">
-        <v>5.92</v>
+        <v>16.18</v>
       </c>
       <c r="M5" t="n">
-        <v>11.24</v>
+        <v>3.76</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1</v>
+        <v>0.59</v>
       </c>
       <c r="O5" t="n">
-        <v>67.84999999999999</v>
-      </c>
-      <c r="P5" t="n">
+        <v>53.41</v>
+      </c>
+      <c r="P5" s="3" t="n">
         <v>28.57142857142857</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="Q5" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>42.85714285714285</v>
+      </c>
+      <c r="S5" s="4" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="T5" s="4" t="n">
         <v>14.28571428571428</v>
       </c>
-      <c r="R5" t="n">
-        <v>100</v>
-      </c>
-      <c r="S5" t="n">
-        <v>71.42857142857143</v>
-      </c>
-      <c r="T5" t="n">
-        <v>42.85714285714285</v>
-      </c>
-      <c r="U5" t="n">
-        <v>20</v>
-      </c>
-      <c r="V5" t="n">
+      <c r="U5" s="2" t="n">
+        <v>83.33333333333334</v>
+      </c>
+      <c r="V5" s="3" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="W5" s="2" t="n">
+        <v>83.33333333333334</v>
+      </c>
+      <c r="X5" s="3" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="Y5" s="4" t="n">
         <v>14.28571428571428</v>
-      </c>
-      <c r="W5" t="n">
-        <v>30</v>
-      </c>
-      <c r="X5" t="n">
-        <v>100</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>21.42857142857143</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Power &amp; Utilities</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>NTPC</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>MARUTI</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Maruti Suzuki India Ltd</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>Mar 2024</t>
         </is>
       </c>
-      <c r="E6" t="n">
-        <v>13.27</v>
-      </c>
-      <c r="F6" t="n">
-        <v>10.58</v>
-      </c>
-      <c r="G6" t="n">
-        <v>11.95</v>
-      </c>
-      <c r="H6" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="I6" t="n">
-        <v>8644</v>
-      </c>
-      <c r="J6" t="n">
-        <v>8.74</v>
-      </c>
-      <c r="K6" t="n">
-        <v>12.22</v>
-      </c>
-      <c r="L6" t="n">
-        <v>8.449999999999999</v>
-      </c>
-      <c r="M6" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="O6" t="n">
-        <v>68.90000000000001</v>
-      </c>
-      <c r="P6" t="n">
+      <c r="E6" s="5" t="n">
+        <v>15.75</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>23.67</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>9.51</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>4936</v>
+      </c>
+      <c r="J6" s="5" t="n">
+        <v>12.01</v>
+      </c>
+      <c r="K6" s="5" t="n">
+        <v>10.51</v>
+      </c>
+      <c r="L6" s="5" t="n">
+        <v>11.14</v>
+      </c>
+      <c r="M6" s="5" t="n">
+        <v>117.91</v>
+      </c>
+      <c r="N6" s="5" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="O6" s="5" t="n">
+        <v>67.33</v>
+      </c>
+      <c r="P6" s="4" t="n">
+        <v>14.28571428571428</v>
+      </c>
+      <c r="Q6" s="3" t="n">
+        <v>33.33333333333333</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>57.14285714285714</v>
+      </c>
+      <c r="S6" s="2" t="n">
+        <v>85.71428571428572</v>
+      </c>
+      <c r="T6" s="3" t="n">
         <v>71.42857142857143</v>
       </c>
-      <c r="Q6" t="n">
-        <v>42.85714285714285</v>
-      </c>
-      <c r="R6" t="n">
-        <v>28.57142857142857</v>
-      </c>
-      <c r="S6" t="n">
-        <v>42.85714285714286</v>
-      </c>
-      <c r="T6" t="n">
+      <c r="U6" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="V6" s="3" t="n">
         <v>71.42857142857143</v>
       </c>
-      <c r="U6" t="n">
-        <v>40</v>
-      </c>
-      <c r="V6" t="n">
-        <v>57.14285714285714</v>
-      </c>
-      <c r="W6" t="n">
-        <v>60</v>
-      </c>
-      <c r="X6" t="n">
-        <v>64.28571428571429</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>71.42857142857143</v>
+      <c r="W6" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="X6" s="2" t="n">
+        <v>85.71428571428571</v>
+      </c>
+      <c r="Y6" s="2" t="n">
+        <v>85.71428571428571</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Power &amp; Utilities</t>
+          <t>TATAMOTORS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>POWERGRID</t>
+          <t>Tata Motors Ltd</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -984,78 +1074,70 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>17.87</v>
+        <v>37.46</v>
       </c>
       <c r="F7" t="n">
-        <v>13.2</v>
+        <v>20.1</v>
       </c>
       <c r="G7" t="n">
-        <v>33.97</v>
+        <v>7.26</v>
       </c>
       <c r="H7" t="n">
-        <v>1.42</v>
+        <v>1.26</v>
       </c>
       <c r="I7" t="n">
-        <v>24176</v>
-      </c>
-      <c r="J7" t="n">
-        <v>9.19</v>
-      </c>
+        <v>45133</v>
+      </c>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="n">
-        <v>5.51</v>
-      </c>
-      <c r="L7" t="n">
-        <v>9.1</v>
-      </c>
+        <v>7.72</v>
+      </c>
+      <c r="L7" t="inlineStr"/>
       <c r="M7" t="n">
-        <v>4.6</v>
+        <v>6.53</v>
       </c>
       <c r="N7" t="n">
-        <v>0.18</v>
+        <v>1.19</v>
       </c>
       <c r="O7" t="n">
-        <v>75.15000000000001</v>
-      </c>
-      <c r="P7" t="n">
-        <v>85.71428571428571</v>
-      </c>
-      <c r="Q7" t="n">
+        <v>62.94</v>
+      </c>
+      <c r="P7" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q7" s="4" t="n">
+        <v>16.66666666666666</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="S7" s="3" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="T7" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" s="3" t="n">
+        <v>42.85714285714285</v>
+      </c>
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" s="3" t="n">
+        <v>42.85714285714285</v>
+      </c>
+      <c r="Y7" s="3" t="n">
         <v>71.42857142857143</v>
-      </c>
-      <c r="R7" t="n">
-        <v>71.42857142857143</v>
-      </c>
-      <c r="S7" t="n">
-        <v>57.14285714285715</v>
-      </c>
-      <c r="T7" t="n">
-        <v>100</v>
-      </c>
-      <c r="U7" t="n">
-        <v>60</v>
-      </c>
-      <c r="V7" t="n">
-        <v>42.85714285714285</v>
-      </c>
-      <c r="W7" t="n">
-        <v>80</v>
-      </c>
-      <c r="X7" t="n">
-        <v>64.28571428571429</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>42.85714285714285</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Power &amp; Utilities</t>
+          <t>TVSMOTOR</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>TATAPOWER</t>
+          <t>TVS Motor Company Ltd</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1069,67 +1151,136 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>13.23</v>
-      </c>
-      <c r="F8" t="n">
-        <v>11.1</v>
-      </c>
+        <v>26.22</v>
+      </c>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="n">
-        <v>6.97</v>
+        <v>4.54</v>
       </c>
       <c r="H8" t="n">
-        <v>1.66</v>
+        <v>3.83</v>
       </c>
       <c r="I8" t="n">
-        <v>3569</v>
+        <v>-2254</v>
       </c>
       <c r="J8" t="n">
-        <v>10.43</v>
+        <v>19.67</v>
       </c>
       <c r="K8" t="n">
-        <v>15.51</v>
+        <v>14.19</v>
       </c>
       <c r="L8" t="n">
-        <v>5.92</v>
+        <v>19.14</v>
       </c>
       <c r="M8" t="n">
-        <v>3.05</v>
+        <v>2.91</v>
       </c>
       <c r="N8" t="n">
-        <v>0.44</v>
+        <v>0.93</v>
       </c>
       <c r="O8" t="n">
-        <v>65.54000000000001</v>
-      </c>
-      <c r="P8" t="n">
-        <v>57.14285714285714</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>57.14285714285714</v>
-      </c>
-      <c r="R8" t="n">
+        <v>50.5</v>
+      </c>
+      <c r="P8" s="3" t="n">
+        <v>71.42857142857143</v>
+      </c>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" s="4" t="n">
         <v>14.28571428571428</v>
       </c>
-      <c r="S8" t="n">
-        <v>14.28571428571429</v>
-      </c>
-      <c r="T8" t="n">
-        <v>57.14285714285714</v>
-      </c>
-      <c r="U8" t="n">
-        <v>80</v>
-      </c>
-      <c r="V8" t="n">
-        <v>71.42857142857143</v>
-      </c>
-      <c r="W8" t="n">
-        <v>30</v>
-      </c>
-      <c r="X8" t="n">
+      <c r="S8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" s="3" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="U8" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="V8" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="W8" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="X8" s="4" t="n">
+        <v>14.28571428571428</v>
+      </c>
+      <c r="Y8" s="3" t="n">
         <v>42.85714285714285</v>
       </c>
-      <c r="Y8" t="n">
-        <v>85.71428571428571</v>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>Median</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="n"/>
+      <c r="C9" s="6" t="n"/>
+      <c r="D9" s="6" t="n"/>
+      <c r="E9" s="6" t="n">
+        <v>22.17</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>28.04</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>9.51</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>3095</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>12.34</v>
+      </c>
+      <c r="K9" s="6" t="n">
+        <v>8.130000000000001</v>
+      </c>
+      <c r="L9" s="6" t="n">
+        <v>11.82</v>
+      </c>
+      <c r="M9" s="6" t="n">
+        <v>47.27</v>
+      </c>
+      <c r="N9" s="6" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="O9" s="6" t="n">
+        <v>67.33</v>
+      </c>
+      <c r="P9" s="6" t="n">
+        <v>57.14</v>
+      </c>
+      <c r="Q9" s="6" t="n">
+        <v>58.33</v>
+      </c>
+      <c r="R9" s="6" t="n">
+        <v>57.14</v>
+      </c>
+      <c r="S9" s="6" t="n">
+        <v>42.86</v>
+      </c>
+      <c r="T9" s="6" t="n">
+        <v>57.14</v>
+      </c>
+      <c r="U9" s="6" t="n">
+        <v>58.33</v>
+      </c>
+      <c r="V9" s="6" t="n">
+        <v>57.14</v>
+      </c>
+      <c r="W9" s="6" t="n">
+        <v>58.33</v>
+      </c>
+      <c r="X9" s="6" t="n">
+        <v>57.14</v>
+      </c>
+      <c r="Y9" s="6" t="n">
+        <v>57.14</v>
       </c>
     </row>
   </sheetData>
@@ -1145,129 +1296,156 @@
   </sheetPr>
   <dimension ref="A1:Y5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="17" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="19" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="20" customWidth="1" min="13" max="13"/>
+    <col width="17" customWidth="1" min="14" max="14"/>
+    <col width="26" customWidth="1" min="15" max="15"/>
+    <col width="34" customWidth="1" min="16" max="16"/>
+    <col width="29" customWidth="1" min="17" max="17"/>
+    <col width="35" customWidth="1" min="18" max="18"/>
+    <col width="28" customWidth="1" min="19" max="19"/>
+    <col width="31" customWidth="1" min="20" max="20"/>
+    <col width="26" customWidth="1" min="21" max="21"/>
+    <col width="30" customWidth="1" min="22" max="22"/>
+    <col width="26" customWidth="1" min="23" max="23"/>
+    <col width="31" customWidth="1" min="24" max="24"/>
+    <col width="28" customWidth="1" min="25" max="25"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>peer_group_name</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>company_id</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>is_benchmark</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>year</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>return_on_equity_pct</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>roce_percentage</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>net_profit_margin_pct</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>debt_to_equity</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>free_cash_flow_cr</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>pat_cagr_5yr</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>revenue_cagr_5yr</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>eps_cagr_5yr</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>interest_coverage</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>asset_turnover</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>composite_quality_score</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>return_on_equity_pct_percentile</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>roce_percentage_percentile</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>net_profit_margin_pct_percentile</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>debt_to_equity_percentile</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>free_cash_flow_cr_percentile</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>pat_cagr_5yr_percentile</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>revenue_cagr_5yr_percentile</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>eps_cagr_5yr_percentile</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>interest_coverage_percentile</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>asset_turnover_percentile</t>
         </is>
@@ -1276,12 +1454,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Life Insurance</t>
+          <t>BANKBARODA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>HDFCLIFE</t>
+          <t>Bank of Baroda</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1295,78 +1473,78 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>10.73</v>
+        <v>15.76</v>
       </c>
       <c r="F2" t="n">
-        <v>6.61</v>
+        <v>6.33</v>
       </c>
       <c r="G2" t="n">
-        <v>1.55</v>
+        <v>15.94</v>
       </c>
       <c r="H2" t="n">
-        <v>0.06</v>
+        <v>12.14</v>
       </c>
       <c r="I2" t="n">
-        <v>-2893</v>
+        <v>-7559</v>
       </c>
       <c r="J2" t="n">
-        <v>4.25</v>
+        <v>74.51000000000001</v>
       </c>
       <c r="K2" t="n">
-        <v>21.17</v>
+        <v>17.48</v>
       </c>
       <c r="L2" t="n">
-        <v>3.13</v>
+        <v>55.18</v>
       </c>
       <c r="M2" t="n">
-        <v>192.29</v>
+        <v>1.9</v>
       </c>
       <c r="N2" t="n">
-        <v>0.34</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="O2" t="n">
-        <v>69.42</v>
-      </c>
-      <c r="P2" t="n">
+        <v>49.07</v>
+      </c>
+      <c r="P2" s="3" t="n">
+        <v>33.33333333333333</v>
+      </c>
+      <c r="Q2" s="3" t="n">
+        <v>66.66666666666666</v>
+      </c>
+      <c r="R2" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="S2" s="3" t="n">
+        <v>33.33333333333334</v>
+      </c>
+      <c r="T2" s="3" t="n">
+        <v>66.66666666666666</v>
+      </c>
+      <c r="U2" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="Q2" t="n">
-        <v>25</v>
-      </c>
-      <c r="R2" t="n">
-        <v>75</v>
-      </c>
-      <c r="S2" t="n">
-        <v>25</v>
-      </c>
-      <c r="T2" t="n">
-        <v>25</v>
-      </c>
-      <c r="U2" t="n">
+      <c r="V2" s="3" t="n">
+        <v>66.66666666666666</v>
+      </c>
+      <c r="W2" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="X2" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="Y2" s="3" t="n">
         <v>50</v>
-      </c>
-      <c r="V2" t="n">
-        <v>75</v>
-      </c>
-      <c r="W2" t="n">
-        <v>66.66666666666666</v>
-      </c>
-      <c r="X2" t="n">
-        <v>50</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>100</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Life Insurance</t>
+          <t>CANBK</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ICICIPRULI</t>
+          <t>Canara Bank</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1380,83 +1558,83 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>7.73</v>
+        <v>16.72</v>
       </c>
       <c r="F3" t="n">
-        <v>8.75</v>
+        <v>6.63</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9399999999999999</v>
+        <v>13.94</v>
       </c>
       <c r="H3" t="n">
-        <v>0.11</v>
+        <v>14.87</v>
       </c>
       <c r="I3" t="n">
-        <v>105</v>
+        <v>13296</v>
       </c>
       <c r="J3" t="n">
-        <v>-5.66</v>
+        <v>85.78</v>
       </c>
       <c r="K3" t="n">
-        <v>16.85</v>
+        <v>18.18</v>
       </c>
       <c r="L3" t="n">
-        <v>-5.59</v>
+        <v>53.42</v>
       </c>
       <c r="M3" t="n">
-        <v>31.02</v>
+        <v>1.61</v>
       </c>
       <c r="N3" t="n">
-        <v>0.3</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="O3" t="n">
-        <v>65.22</v>
-      </c>
-      <c r="P3" t="n">
-        <v>25</v>
-      </c>
-      <c r="Q3" t="n">
+        <v>59.34</v>
+      </c>
+      <c r="P3" s="3" t="n">
+        <v>66.66666666666666</v>
+      </c>
+      <c r="Q3" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>66.66666666666666</v>
+      </c>
+      <c r="S3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="U3" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="V3" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="W3" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="R3" t="n">
-        <v>25</v>
-      </c>
-      <c r="S3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T3" t="n">
-        <v>75</v>
-      </c>
-      <c r="U3" t="n">
-        <v>25</v>
-      </c>
-      <c r="V3" t="n">
-        <v>50</v>
-      </c>
-      <c r="W3" t="n">
-        <v>33.33333333333333</v>
-      </c>
-      <c r="X3" t="n">
-        <v>25</v>
-      </c>
-      <c r="Y3" t="n">
+      <c r="X3" s="3" t="n">
+        <v>66.66666666666666</v>
+      </c>
+      <c r="Y3" s="3" t="n">
         <v>50</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Life Insurance</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>LICI</t>
+          <t>Punjab National Bank</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1465,148 +1643,132 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>49.45</v>
+        <v>61.32</v>
       </c>
       <c r="F4" t="n">
-        <v>63.79</v>
+        <v>1.63</v>
       </c>
       <c r="G4" t="n">
-        <v>4.84</v>
+        <v>8.4</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="I4" t="n">
-        <v>853</v>
-      </c>
-      <c r="J4" t="n">
-        <v>73.18000000000001</v>
-      </c>
+        <v>-29445</v>
+      </c>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="n">
-        <v>8.16</v>
+        <v>15.9</v>
       </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
-        <v>371.94</v>
+        <v>0.21</v>
       </c>
       <c r="N4" t="n">
-        <v>0.16</v>
+        <v>1.51</v>
       </c>
       <c r="O4" t="n">
-        <v>69.53</v>
-      </c>
-      <c r="P4" t="n">
-        <v>100</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>100</v>
-      </c>
-      <c r="R4" t="n">
-        <v>100</v>
-      </c>
-      <c r="S4" t="n">
-        <v>62.5</v>
-      </c>
-      <c r="T4" t="n">
-        <v>100</v>
-      </c>
-      <c r="U4" t="n">
-        <v>100</v>
-      </c>
-      <c r="V4" t="n">
-        <v>25</v>
+        <v>64.92</v>
+      </c>
+      <c r="P4" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q4" s="3" t="n">
+        <v>33.33333333333333</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>33.33333333333333</v>
+      </c>
+      <c r="S4" s="3" t="n">
+        <v>66.66666666666667</v>
+      </c>
+      <c r="T4" s="3" t="n">
+        <v>33.33333333333333</v>
+      </c>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" s="3" t="n">
+        <v>33.33333333333333</v>
       </c>
       <c r="W4" t="inlineStr"/>
-      <c r="X4" t="n">
-        <v>100</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>25</v>
+      <c r="X4" s="3" t="n">
+        <v>33.33333333333333</v>
+      </c>
+      <c r="Y4" s="2" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Life Insurance</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>SBILIFE</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Mar 2024</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>12.7</v>
-      </c>
-      <c r="F5" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="G5" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="n">
-        <v>-2099</v>
-      </c>
-      <c r="J5" t="n">
-        <v>7.37</v>
-      </c>
-      <c r="K5" t="n">
-        <v>24.23</v>
-      </c>
-      <c r="L5" t="n">
-        <v>7.89</v>
-      </c>
-      <c r="M5" t="n">
-        <v>240.33</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="O5" t="n">
-        <v>55.2</v>
-      </c>
-      <c r="P5" t="n">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Median</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n"/>
+      <c r="C5" s="6" t="n"/>
+      <c r="D5" s="6" t="n"/>
+      <c r="E5" s="6" t="n">
+        <v>16.72</v>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>6.33</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>13.94</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>12.14</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>-7559</v>
+      </c>
+      <c r="J5" s="6" t="n">
+        <v>80.15000000000001</v>
+      </c>
+      <c r="K5" s="6" t="n">
+        <v>17.48</v>
+      </c>
+      <c r="L5" s="6" t="n">
+        <v>54.3</v>
+      </c>
+      <c r="M5" s="6" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="N5" s="6" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="O5" s="6" t="n">
+        <v>59.34</v>
+      </c>
+      <c r="P5" s="6" t="n">
+        <v>66.67</v>
+      </c>
+      <c r="Q5" s="6" t="n">
+        <v>66.67</v>
+      </c>
+      <c r="R5" s="6" t="n">
+        <v>66.67</v>
+      </c>
+      <c r="S5" s="6" t="n">
+        <v>33.33</v>
+      </c>
+      <c r="T5" s="6" t="n">
+        <v>66.67</v>
+      </c>
+      <c r="U5" s="6" t="n">
         <v>75</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="V5" s="6" t="n">
+        <v>66.67</v>
+      </c>
+      <c r="W5" s="6" t="n">
         <v>75</v>
       </c>
-      <c r="R5" t="n">
+      <c r="X5" s="6" t="n">
+        <v>66.67</v>
+      </c>
+      <c r="Y5" s="6" t="n">
         <v>50</v>
-      </c>
-      <c r="S5" t="n">
-        <v>62.5</v>
-      </c>
-      <c r="T5" t="n">
-        <v>50</v>
-      </c>
-      <c r="U5" t="n">
-        <v>75</v>
-      </c>
-      <c r="V5" t="n">
-        <v>100</v>
-      </c>
-      <c r="W5" t="n">
-        <v>100</v>
-      </c>
-      <c r="X5" t="n">
-        <v>75</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>75</v>
       </c>
     </row>
   </sheetData>
@@ -1620,131 +1782,158 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y5"/>
+  <dimension ref="A1:Y6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="27" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="17" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="19" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="20" customWidth="1" min="13" max="13"/>
+    <col width="17" customWidth="1" min="14" max="14"/>
+    <col width="26" customWidth="1" min="15" max="15"/>
+    <col width="34" customWidth="1" min="16" max="16"/>
+    <col width="29" customWidth="1" min="17" max="17"/>
+    <col width="35" customWidth="1" min="18" max="18"/>
+    <col width="28" customWidth="1" min="19" max="19"/>
+    <col width="31" customWidth="1" min="20" max="20"/>
+    <col width="26" customWidth="1" min="21" max="21"/>
+    <col width="30" customWidth="1" min="22" max="22"/>
+    <col width="26" customWidth="1" min="23" max="23"/>
+    <col width="31" customWidth="1" min="24" max="24"/>
+    <col width="28" customWidth="1" min="25" max="25"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>peer_group_name</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>company_id</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>is_benchmark</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>year</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>return_on_equity_pct</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>roce_percentage</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>net_profit_margin_pct</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>debt_to_equity</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>free_cash_flow_cr</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>pat_cagr_5yr</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>revenue_cagr_5yr</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>eps_cagr_5yr</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>interest_coverage</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>asset_turnover</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>composite_quality_score</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>return_on_equity_pct_percentile</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>roce_percentage_percentile</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>net_profit_margin_pct_percentile</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>debt_to_equity_percentile</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>free_cash_flow_cr_percentile</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>pat_cagr_5yr_percentile</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>revenue_cagr_5yr_percentile</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>eps_cagr_5yr_percentile</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>interest_coverage_percentile</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>asset_turnover_percentile</t>
         </is>
@@ -1753,12 +1942,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Steel</t>
+          <t>HINDALCO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>HINDALCO</t>
+          <t>Hindalco Industries Ltd</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1804,46 +1993,46 @@
       <c r="O2" t="n">
         <v>69.38</v>
       </c>
-      <c r="P2" t="n">
+      <c r="P2" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="Q2" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="R2" t="n">
+      <c r="R2" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="S2" t="n">
+      <c r="S2" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="T2" t="n">
-        <v>100</v>
-      </c>
-      <c r="U2" t="n">
-        <v>100</v>
-      </c>
-      <c r="V2" t="n">
+      <c r="T2" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="U2" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="V2" s="2" t="n">
         <v>75</v>
       </c>
-      <c r="W2" t="n">
-        <v>100</v>
-      </c>
-      <c r="X2" t="n">
-        <v>100</v>
-      </c>
-      <c r="Y2" t="n">
+      <c r="W2" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="X2" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="Y2" s="2" t="n">
         <v>100</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Steel</t>
+          <t>JINDALSTEL</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>JINDALSTEL</t>
+          <t>Jindal Steel &amp; Power Ltd</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1885,42 +2074,42 @@
       <c r="O3" t="n">
         <v>63.6</v>
       </c>
-      <c r="P3" t="n">
-        <v>100</v>
-      </c>
-      <c r="Q3" t="n">
+      <c r="P3" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q3" s="2" t="n">
         <v>75</v>
       </c>
-      <c r="R3" t="n">
-        <v>100</v>
-      </c>
-      <c r="S3" t="n">
+      <c r="R3" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="S3" s="2" t="n">
         <v>75</v>
       </c>
-      <c r="T3" t="n">
+      <c r="T3" s="3" t="n">
         <v>50</v>
       </c>
       <c r="U3" t="inlineStr"/>
-      <c r="V3" t="n">
+      <c r="V3" s="4" t="n">
         <v>25</v>
       </c>
       <c r="W3" t="inlineStr"/>
-      <c r="X3" t="n">
+      <c r="X3" s="2" t="n">
         <v>75</v>
       </c>
-      <c r="Y3" t="n">
+      <c r="Y3" s="4" t="n">
         <v>25</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Steel</t>
+          <t>JSWSTEEL</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>JSWSTEEL</t>
+          <t>JSW Steel Ltd</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1966,112 +2155,186 @@
       <c r="O4" t="n">
         <v>60.28</v>
       </c>
-      <c r="P4" t="n">
+      <c r="P4" s="2" t="n">
         <v>75</v>
       </c>
-      <c r="Q4" t="n">
-        <v>100</v>
-      </c>
-      <c r="R4" t="n">
+      <c r="Q4" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="R4" s="2" t="n">
         <v>75</v>
       </c>
-      <c r="S4" t="n">
+      <c r="S4" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="T4" t="n">
+      <c r="T4" s="4" t="n">
         <v>25</v>
       </c>
-      <c r="U4" t="n">
+      <c r="U4" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="V4" t="n">
-        <v>100</v>
-      </c>
-      <c r="W4" t="n">
+      <c r="V4" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="W4" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="X4" t="n">
+      <c r="X4" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="Y4" t="n">
+      <c r="Y4" s="3" t="n">
         <v>50</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Steel</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>TATASTEEL</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tata Steel Ltd
+</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>Mar 2024</t>
         </is>
       </c>
-      <c r="E5" t="n">
+      <c r="E5" s="5" t="n">
         <v>-5.33</v>
       </c>
-      <c r="F5" t="n">
+      <c r="F5" s="5" t="n">
         <v>7.02</v>
       </c>
-      <c r="G5" t="n">
+      <c r="G5" s="5" t="n">
         <v>-2.14</v>
       </c>
-      <c r="H5" t="n">
+      <c r="H5" s="5" t="n">
         <v>0.95</v>
       </c>
-      <c r="I5" t="n">
+      <c r="I5" s="5" t="n">
         <v>6048</v>
       </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="n">
+      <c r="J5" s="5" t="inlineStr"/>
+      <c r="K5" s="5" t="n">
         <v>7.77</v>
       </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="n">
+      <c r="L5" s="5" t="inlineStr"/>
+      <c r="M5" s="5" t="n">
         <v>2.16</v>
       </c>
-      <c r="N5" t="n">
+      <c r="N5" s="5" t="n">
         <v>0.85</v>
       </c>
-      <c r="O5" t="n">
+      <c r="O5" s="5" t="n">
         <v>52.68</v>
       </c>
-      <c r="P5" t="n">
+      <c r="P5" s="4" t="n">
         <v>25</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="Q5" s="4" t="n">
         <v>25</v>
       </c>
-      <c r="R5" t="n">
+      <c r="R5" s="4" t="n">
         <v>25</v>
       </c>
-      <c r="S5" t="n">
+      <c r="S5" s="4" t="n">
         <v>25</v>
       </c>
-      <c r="T5" t="n">
+      <c r="T5" s="2" t="n">
         <v>75</v>
       </c>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="n">
+      <c r="U5" s="5" t="inlineStr"/>
+      <c r="V5" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="W5" t="inlineStr"/>
-      <c r="X5" t="n">
+      <c r="W5" s="5" t="inlineStr"/>
+      <c r="X5" s="4" t="n">
         <v>25</v>
       </c>
-      <c r="Y5" t="n">
+      <c r="Y5" s="2" t="n">
         <v>75</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Median</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n"/>
+      <c r="C6" s="6" t="n"/>
+      <c r="D6" s="6" t="n"/>
+      <c r="E6" s="6" t="n">
+        <v>10.56</v>
+      </c>
+      <c r="F6" s="6" t="n">
+        <v>12.25</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>4.92</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>1856</v>
+      </c>
+      <c r="J6" s="6" t="n">
+        <v>8.33</v>
+      </c>
+      <c r="K6" s="6" t="n">
+        <v>9.18</v>
+      </c>
+      <c r="L6" s="6" t="n">
+        <v>7.89</v>
+      </c>
+      <c r="M6" s="6" t="n">
+        <v>5.83</v>
+      </c>
+      <c r="N6" s="6" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="O6" s="6" t="n">
+        <v>61.94</v>
+      </c>
+      <c r="P6" s="6" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="Q6" s="6" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="R6" s="6" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="S6" s="6" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="T6" s="6" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="U6" s="6" t="n">
+        <v>75</v>
+      </c>
+      <c r="V6" s="6" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="W6" s="6" t="n">
+        <v>75</v>
+      </c>
+      <c r="X6" s="6" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="Y6" s="6" t="n">
+        <v>62.5</v>
       </c>
     </row>
   </sheetData>
@@ -2085,235 +2348,262 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y6"/>
+  <dimension ref="A1:Y5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="49" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="17" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="19" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="20" customWidth="1" min="13" max="13"/>
+    <col width="17" customWidth="1" min="14" max="14"/>
+    <col width="26" customWidth="1" min="15" max="15"/>
+    <col width="34" customWidth="1" min="16" max="16"/>
+    <col width="29" customWidth="1" min="17" max="17"/>
+    <col width="35" customWidth="1" min="18" max="18"/>
+    <col width="28" customWidth="1" min="19" max="19"/>
+    <col width="31" customWidth="1" min="20" max="20"/>
+    <col width="26" customWidth="1" min="21" max="21"/>
+    <col width="30" customWidth="1" min="22" max="22"/>
+    <col width="26" customWidth="1" min="23" max="23"/>
+    <col width="31" customWidth="1" min="24" max="24"/>
+    <col width="28" customWidth="1" min="25" max="25"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>peer_group_name</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>company_id</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>is_benchmark</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>year</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>return_on_equity_pct</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>roce_percentage</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>net_profit_margin_pct</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>debt_to_equity</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>free_cash_flow_cr</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>pat_cagr_5yr</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>revenue_cagr_5yr</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>eps_cagr_5yr</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>interest_coverage</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>asset_turnover</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>composite_quality_score</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>return_on_equity_pct_percentile</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>roce_percentage_percentile</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>net_profit_margin_pct_percentile</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>debt_to_equity_percentile</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>free_cash_flow_cr_percentile</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>pat_cagr_5yr_percentile</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>revenue_cagr_5yr_percentile</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>eps_cagr_5yr_percentile</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>interest_coverage_percentile</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>asset_turnover_percentile</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Private Banks</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>AXISBANK</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>BAJFINANCE</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>Bajaj Finance Ltd</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
         <is>
           <t>Mar 2024</t>
         </is>
       </c>
-      <c r="E2" t="n">
-        <v>15.83</v>
-      </c>
-      <c r="F2" t="n">
-        <v>7.06</v>
-      </c>
-      <c r="G2" t="n">
-        <v>22.73</v>
-      </c>
-      <c r="H2" t="n">
-        <v>8.25</v>
-      </c>
-      <c r="I2" t="n">
-        <v>-14556</v>
-      </c>
-      <c r="J2" t="n">
-        <v>39.67</v>
-      </c>
-      <c r="K2" t="n">
-        <v>14.74</v>
-      </c>
-      <c r="L2" t="n">
-        <v>35.1</v>
-      </c>
-      <c r="M2" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="O2" t="n">
-        <v>60.76</v>
-      </c>
-      <c r="P2" t="n">
-        <v>80</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>20</v>
-      </c>
-      <c r="R2" t="n">
-        <v>40</v>
-      </c>
-      <c r="S2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T2" t="n">
-        <v>40</v>
-      </c>
-      <c r="U2" t="n">
-        <v>80</v>
-      </c>
-      <c r="V2" t="n">
-        <v>40</v>
-      </c>
-      <c r="W2" t="n">
-        <v>80</v>
-      </c>
-      <c r="X2" t="n">
-        <v>80</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>50</v>
+      <c r="E2" s="5" t="n">
+        <v>18.84</v>
+      </c>
+      <c r="F2" s="5" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="G2" s="5" t="n">
+        <v>26.29</v>
+      </c>
+      <c r="H2" s="5" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="I2" s="5" t="n">
+        <v>-79931</v>
+      </c>
+      <c r="J2" s="5" t="n">
+        <v>29.32</v>
+      </c>
+      <c r="K2" s="5" t="n">
+        <v>24.35</v>
+      </c>
+      <c r="L2" s="5" t="n">
+        <v>27.56</v>
+      </c>
+      <c r="M2" s="5" t="n">
+        <v>2689.17</v>
+      </c>
+      <c r="N2" s="5" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="O2" s="5" t="n">
+        <v>57.47</v>
+      </c>
+      <c r="P2" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q2" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="R2" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="S2" s="3" t="n">
+        <v>66.66666666666667</v>
+      </c>
+      <c r="T2" s="3" t="n">
+        <v>33.33333333333333</v>
+      </c>
+      <c r="U2" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="V2" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="W2" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="X2" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="Y2" s="2" t="n">
+        <v>83.33333333333334</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Private Banks</t>
+          <t>CHOLAFIN</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>HDFCBANK</t>
+          <t>Cholamandalam Investment &amp; Finance Company Ltd</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -2322,78 +2612,79 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>14.34</v>
+        <v>17.46</v>
       </c>
       <c r="F3" t="n">
-        <v>7.67</v>
+        <v>10.4</v>
       </c>
       <c r="G3" t="n">
-        <v>23.07</v>
+        <v>17.85</v>
       </c>
       <c r="H3" t="n">
-        <v>6.81</v>
+        <v>6.86</v>
       </c>
       <c r="I3" t="n">
-        <v>35669</v>
+        <v>-38538</v>
       </c>
       <c r="J3" t="n">
-        <v>23.87</v>
+        <v>23.36</v>
       </c>
       <c r="K3" t="n">
-        <v>21.95</v>
+        <v>21.94</v>
       </c>
       <c r="L3" t="n">
-        <v>15.42</v>
+        <v>22.28</v>
       </c>
       <c r="M3" t="n">
-        <v>1.4</v>
+        <v>21.21</v>
       </c>
       <c r="N3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.12</v>
       </c>
       <c r="O3" t="n">
-        <v>49.05</v>
-      </c>
-      <c r="P3" t="n">
-        <v>60</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>60</v>
-      </c>
-      <c r="R3" t="n">
-        <v>60</v>
-      </c>
-      <c r="S3" t="n">
-        <v>40</v>
-      </c>
-      <c r="T3" t="n">
-        <v>100</v>
-      </c>
-      <c r="U3" t="n">
-        <v>60</v>
-      </c>
-      <c r="V3" t="n">
-        <v>100</v>
-      </c>
-      <c r="W3" t="n">
-        <v>20</v>
-      </c>
-      <c r="X3" t="n">
-        <v>60</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>50</v>
+        <v>48.86</v>
+      </c>
+      <c r="P3" s="3" t="n">
+        <v>66.66666666666666</v>
+      </c>
+      <c r="Q3" s="3" t="n">
+        <v>33.33333333333333</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>33.33333333333333</v>
+      </c>
+      <c r="S3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" s="3" t="n">
+        <v>66.66666666666666</v>
+      </c>
+      <c r="U3" s="3" t="n">
+        <v>33.33333333333333</v>
+      </c>
+      <c r="V3" s="3" t="n">
+        <v>66.66666666666666</v>
+      </c>
+      <c r="W3" s="3" t="n">
+        <v>66.66666666666666</v>
+      </c>
+      <c r="X3" s="3" t="n">
+        <v>66.66666666666666</v>
+      </c>
+      <c r="Y3" s="3" t="n">
+        <v>33.33333333333333</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Private Banks</t>
+          <t>SHRIRAMFIN</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ICICIBANK</t>
+          <t xml:space="preserve">Shriram Finance Ltd
+</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -2407,237 +2698,140 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>17.99</v>
+        <v>15.12</v>
       </c>
       <c r="F4" t="n">
-        <v>7.6</v>
+        <v>11.3</v>
       </c>
       <c r="G4" t="n">
-        <v>28.89</v>
+        <v>20.33</v>
       </c>
       <c r="H4" t="n">
-        <v>6.45</v>
+        <v>3.99</v>
       </c>
       <c r="I4" t="n">
-        <v>12547</v>
+        <v>-31359</v>
       </c>
       <c r="J4" t="n">
-        <v>51.95</v>
+        <v>23.49</v>
       </c>
       <c r="K4" t="n">
-        <v>17.25</v>
+        <v>18.56</v>
       </c>
       <c r="L4" t="n">
-        <v>55.18</v>
+        <v>14.29</v>
       </c>
       <c r="M4" t="n">
-        <v>1.3</v>
+        <v>0.68</v>
       </c>
       <c r="N4" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.15</v>
       </c>
       <c r="O4" t="n">
-        <v>63.6</v>
-      </c>
-      <c r="P4" t="n">
-        <v>100</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>40</v>
-      </c>
-      <c r="R4" t="n">
-        <v>80</v>
-      </c>
-      <c r="S4" t="n">
-        <v>60</v>
-      </c>
-      <c r="T4" t="n">
-        <v>80</v>
-      </c>
-      <c r="U4" t="n">
-        <v>100</v>
-      </c>
-      <c r="V4" t="n">
-        <v>80</v>
-      </c>
-      <c r="W4" t="n">
-        <v>100</v>
-      </c>
-      <c r="X4" t="n">
-        <v>40</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>50</v>
+        <v>53.19</v>
+      </c>
+      <c r="P4" s="3" t="n">
+        <v>33.33333333333333</v>
+      </c>
+      <c r="Q4" s="3" t="n">
+        <v>66.66666666666666</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>66.66666666666666</v>
+      </c>
+      <c r="S4" s="3" t="n">
+        <v>33.33333333333334</v>
+      </c>
+      <c r="T4" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="U4" s="3" t="n">
+        <v>66.66666666666666</v>
+      </c>
+      <c r="V4" s="3" t="n">
+        <v>33.33333333333333</v>
+      </c>
+      <c r="W4" s="3" t="n">
+        <v>33.33333333333333</v>
+      </c>
+      <c r="X4" s="3" t="n">
+        <v>33.33333333333333</v>
+      </c>
+      <c r="Y4" s="2" t="n">
+        <v>83.33333333333334</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Private Banks</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>INDUSINDBK</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Mar 2024</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>14.25</v>
-      </c>
-      <c r="F5" t="n">
-        <v>7.93</v>
-      </c>
-      <c r="G5" t="n">
-        <v>19.56</v>
-      </c>
-      <c r="H5" t="n">
-        <v>6.89</v>
-      </c>
-      <c r="I5" t="n">
-        <v>-17468</v>
-      </c>
-      <c r="J5" t="n">
-        <v>22.08</v>
-      </c>
-      <c r="K5" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="L5" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="M5" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="O5" t="n">
-        <v>52.45</v>
-      </c>
-      <c r="P5" t="n">
-        <v>40</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>100</v>
-      </c>
-      <c r="R5" t="n">
-        <v>20</v>
-      </c>
-      <c r="S5" t="n">
-        <v>20</v>
-      </c>
-      <c r="T5" t="n">
-        <v>20</v>
-      </c>
-      <c r="U5" t="n">
-        <v>40</v>
-      </c>
-      <c r="V5" t="n">
-        <v>60</v>
-      </c>
-      <c r="W5" t="n">
-        <v>40</v>
-      </c>
-      <c r="X5" t="n">
-        <v>100</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Private Banks</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>KOTAKBANK</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Mar 2024</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>14.01</v>
-      </c>
-      <c r="F6" t="n">
-        <v>7.86</v>
-      </c>
-      <c r="G6" t="n">
-        <v>32.39</v>
-      </c>
-      <c r="H6" t="n">
-        <v>4</v>
-      </c>
-      <c r="I6" t="n">
-        <v>6766</v>
-      </c>
-      <c r="J6" t="n">
-        <v>20.38</v>
-      </c>
-      <c r="K6" t="n">
-        <v>13.52</v>
-      </c>
-      <c r="L6" t="n">
-        <v>19.34</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="O6" t="n">
-        <v>65.58</v>
-      </c>
-      <c r="P6" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>80</v>
-      </c>
-      <c r="R6" t="n">
-        <v>100</v>
-      </c>
-      <c r="S6" t="n">
-        <v>80</v>
-      </c>
-      <c r="T6" t="n">
-        <v>60</v>
-      </c>
-      <c r="U6" t="n">
-        <v>20</v>
-      </c>
-      <c r="V6" t="n">
-        <v>20</v>
-      </c>
-      <c r="W6" t="n">
-        <v>60</v>
-      </c>
-      <c r="X6" t="n">
-        <v>20</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>50</v>
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Median</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n"/>
+      <c r="C5" s="6" t="n"/>
+      <c r="D5" s="6" t="n"/>
+      <c r="E5" s="6" t="n">
+        <v>17.46</v>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>20.33</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>3.99</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>-38538</v>
+      </c>
+      <c r="J5" s="6" t="n">
+        <v>23.49</v>
+      </c>
+      <c r="K5" s="6" t="n">
+        <v>21.94</v>
+      </c>
+      <c r="L5" s="6" t="n">
+        <v>22.28</v>
+      </c>
+      <c r="M5" s="6" t="n">
+        <v>21.21</v>
+      </c>
+      <c r="N5" s="6" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="O5" s="6" t="n">
+        <v>53.19</v>
+      </c>
+      <c r="P5" s="6" t="n">
+        <v>66.67</v>
+      </c>
+      <c r="Q5" s="6" t="n">
+        <v>66.67</v>
+      </c>
+      <c r="R5" s="6" t="n">
+        <v>66.67</v>
+      </c>
+      <c r="S5" s="6" t="n">
+        <v>33.33</v>
+      </c>
+      <c r="T5" s="6" t="n">
+        <v>66.67</v>
+      </c>
+      <c r="U5" s="6" t="n">
+        <v>66.67</v>
+      </c>
+      <c r="V5" s="6" t="n">
+        <v>66.67</v>
+      </c>
+      <c r="W5" s="6" t="n">
+        <v>66.67</v>
+      </c>
+      <c r="X5" s="6" t="n">
+        <v>66.67</v>
+      </c>
+      <c r="Y5" s="6" t="n">
+        <v>83.33</v>
       </c>
     </row>
   </sheetData>
@@ -2651,131 +2845,158 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y8"/>
+  <dimension ref="A1:Y9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="31" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="17" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="19" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="20" customWidth="1" min="13" max="13"/>
+    <col width="17" customWidth="1" min="14" max="14"/>
+    <col width="26" customWidth="1" min="15" max="15"/>
+    <col width="34" customWidth="1" min="16" max="16"/>
+    <col width="29" customWidth="1" min="17" max="17"/>
+    <col width="35" customWidth="1" min="18" max="18"/>
+    <col width="28" customWidth="1" min="19" max="19"/>
+    <col width="31" customWidth="1" min="20" max="20"/>
+    <col width="26" customWidth="1" min="21" max="21"/>
+    <col width="30" customWidth="1" min="22" max="22"/>
+    <col width="26" customWidth="1" min="23" max="23"/>
+    <col width="31" customWidth="1" min="24" max="24"/>
+    <col width="28" customWidth="1" min="25" max="25"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>peer_group_name</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>company_id</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>is_benchmark</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>year</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>return_on_equity_pct</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>roce_percentage</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>net_profit_margin_pct</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>debt_to_equity</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>free_cash_flow_cr</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>pat_cagr_5yr</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>revenue_cagr_5yr</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>eps_cagr_5yr</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>interest_coverage</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>asset_turnover</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>composite_quality_score</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>return_on_equity_pct_percentile</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>roce_percentage_percentile</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>net_profit_margin_pct_percentile</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>debt_to_equity_percentile</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>free_cash_flow_cr_percentile</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>pat_cagr_5yr_percentile</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>revenue_cagr_5yr_percentile</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>eps_cagr_5yr_percentile</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>interest_coverage_percentile</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>asset_turnover_percentile</t>
         </is>
@@ -2784,12 +3005,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Automobiles</t>
+          <t>BRITANNIA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>BAJAJ-AUTO</t>
+          <t>Britannia Industries Ltd</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -2803,78 +3024,78 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>26.61</v>
+        <v>54.15</v>
       </c>
       <c r="F2" t="n">
-        <v>33.5</v>
+        <v>48.9</v>
       </c>
       <c r="G2" t="n">
-        <v>17.18</v>
+        <v>12.73</v>
       </c>
       <c r="H2" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.52</v>
       </c>
       <c r="I2" t="n">
-        <v>6486</v>
+        <v>3050</v>
       </c>
       <c r="J2" t="n">
-        <v>9.359999999999999</v>
+        <v>13.06</v>
       </c>
       <c r="K2" t="n">
-        <v>8.130000000000001</v>
+        <v>8.69</v>
       </c>
       <c r="L2" t="n">
-        <v>10.18</v>
+        <v>13.14</v>
       </c>
       <c r="M2" t="n">
-        <v>174.42</v>
+        <v>20.6</v>
       </c>
       <c r="N2" t="n">
-        <v>1.14</v>
+        <v>1.85</v>
       </c>
       <c r="O2" t="n">
-        <v>75.48</v>
-      </c>
-      <c r="P2" t="n">
+        <v>83.70999999999999</v>
+      </c>
+      <c r="P2" s="2" t="n">
         <v>85.71428571428571</v>
       </c>
-      <c r="Q2" t="n">
-        <v>100</v>
-      </c>
-      <c r="R2" t="n">
+      <c r="Q2" s="2" t="n">
         <v>85.71428571428571</v>
       </c>
-      <c r="S2" t="n">
-        <v>42.85714285714286</v>
-      </c>
-      <c r="T2" t="n">
+      <c r="R2" s="3" t="n">
+        <v>42.85714285714285</v>
+      </c>
+      <c r="S2" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" s="3" t="n">
+        <v>71.42857142857143</v>
+      </c>
+      <c r="U2" s="3" t="n">
+        <v>66.66666666666666</v>
+      </c>
+      <c r="V2" s="3" t="n">
+        <v>57.14285714285714</v>
+      </c>
+      <c r="W2" s="3" t="n">
+        <v>66.66666666666666</v>
+      </c>
+      <c r="X2" s="3" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="Y2" s="2" t="n">
         <v>85.71428571428571</v>
-      </c>
-      <c r="U2" t="n">
-        <v>33.33333333333333</v>
-      </c>
-      <c r="V2" t="n">
-        <v>57.14285714285714</v>
-      </c>
-      <c r="W2" t="n">
-        <v>33.33333333333333</v>
-      </c>
-      <c r="X2" t="n">
-        <v>100</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>57.14285714285714</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Automobiles</t>
+          <t>DABUR</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>EICHERMOT</t>
+          <t>Dabur India Ltd</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -2888,78 +3109,78 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>22.17</v>
+        <v>18.36</v>
       </c>
       <c r="F3" t="n">
-        <v>31.1</v>
+        <v>22.3</v>
       </c>
       <c r="G3" t="n">
-        <v>24.2</v>
+        <v>14.6</v>
       </c>
       <c r="H3" t="n">
-        <v>0.02</v>
+        <v>0.14</v>
       </c>
       <c r="I3" t="n">
-        <v>890</v>
+        <v>1042</v>
       </c>
       <c r="J3" t="n">
-        <v>12.68</v>
+        <v>4.6</v>
       </c>
       <c r="K3" t="n">
-        <v>11.04</v>
+        <v>7.81</v>
       </c>
       <c r="L3" t="n">
-        <v>12.51</v>
+        <v>4.56</v>
       </c>
       <c r="M3" t="n">
-        <v>114.71</v>
+        <v>23.24</v>
       </c>
       <c r="N3" t="n">
-        <v>0.72</v>
+        <v>0.82</v>
       </c>
       <c r="O3" t="n">
-        <v>72.52</v>
-      </c>
-      <c r="P3" t="n">
+        <v>72.03</v>
+      </c>
+      <c r="P3" s="3" t="n">
+        <v>42.85714285714285</v>
+      </c>
+      <c r="Q3" s="3" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="R3" s="3" t="n">
         <v>57.14285714285714</v>
       </c>
-      <c r="Q3" t="n">
-        <v>83.33333333333334</v>
-      </c>
-      <c r="R3" t="n">
-        <v>100</v>
-      </c>
-      <c r="S3" t="n">
+      <c r="S3" s="3" t="n">
+        <v>42.85714285714286</v>
+      </c>
+      <c r="T3" s="3" t="n">
+        <v>42.85714285714285</v>
+      </c>
+      <c r="U3" s="4" t="n">
+        <v>16.66666666666666</v>
+      </c>
+      <c r="V3" s="3" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="W3" s="4" t="n">
+        <v>16.66666666666666</v>
+      </c>
+      <c r="X3" s="3" t="n">
+        <v>42.85714285714285</v>
+      </c>
+      <c r="Y3" s="3" t="n">
         <v>71.42857142857143</v>
-      </c>
-      <c r="T3" t="n">
-        <v>42.85714285714285</v>
-      </c>
-      <c r="U3" t="n">
-        <v>66.66666666666666</v>
-      </c>
-      <c r="V3" t="n">
-        <v>85.71428571428571</v>
-      </c>
-      <c r="W3" t="n">
-        <v>66.66666666666666</v>
-      </c>
-      <c r="X3" t="n">
-        <v>71.42857142857143</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>28.57142857142857</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Automobiles</t>
+          <t>GODREJCP</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>HEROMOTOCO</t>
+          <t>Godrej Consumer Products Ltd</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -2973,168 +3194,162 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>21.14</v>
+        <v>-4.45</v>
       </c>
       <c r="F4" t="n">
-        <v>29.1</v>
+        <v>26.49</v>
       </c>
       <c r="G4" t="n">
-        <v>9.9</v>
+        <v>-3.98</v>
       </c>
       <c r="H4" t="n">
-        <v>0.03</v>
+        <v>0.26</v>
       </c>
       <c r="I4" t="n">
-        <v>3095</v>
-      </c>
-      <c r="J4" t="n">
-        <v>1.54</v>
-      </c>
+        <v>-1365</v>
+      </c>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="L4" t="n">
-        <v>1.69</v>
-      </c>
+        <v>6.45</v>
+      </c>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
-        <v>47.27</v>
+        <v>2.41</v>
       </c>
       <c r="N4" t="n">
-        <v>1.44</v>
+        <v>0.77</v>
       </c>
       <c r="O4" t="n">
-        <v>72.03</v>
-      </c>
-      <c r="P4" t="n">
+        <v>58.78</v>
+      </c>
+      <c r="P4" s="4" t="n">
+        <v>14.28571428571428</v>
+      </c>
+      <c r="Q4" s="3" t="n">
         <v>42.85714285714285</v>
       </c>
-      <c r="Q4" t="n">
-        <v>66.66666666666666</v>
-      </c>
-      <c r="R4" t="n">
-        <v>71.42857142857143</v>
-      </c>
-      <c r="S4" t="n">
-        <v>57.14285714285715</v>
-      </c>
-      <c r="T4" t="n">
-        <v>57.14285714285714</v>
-      </c>
-      <c r="U4" t="n">
-        <v>16.66666666666666</v>
-      </c>
-      <c r="V4" t="n">
+      <c r="R4" s="4" t="n">
         <v>14.28571428571428</v>
       </c>
-      <c r="W4" t="n">
-        <v>16.66666666666666</v>
-      </c>
-      <c r="X4" t="n">
-        <v>57.14285714285714</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>100</v>
+      <c r="S4" s="4" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="T4" s="4" t="n">
+        <v>14.28571428571428</v>
+      </c>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" s="4" t="n">
+        <v>14.28571428571428</v>
+      </c>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" s="4" t="n">
+        <v>14.28571428571428</v>
+      </c>
+      <c r="Y4" s="3" t="n">
+        <v>35.71428571428572</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Automobiles</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>M&amp;M</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>HINDUNILVR</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hindustan Unilever Ltd
+</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>Mar 2024</t>
         </is>
       </c>
-      <c r="E5" t="n">
-        <v>18.54</v>
-      </c>
-      <c r="F5" t="n">
-        <v>26.98</v>
-      </c>
-      <c r="G5" t="n">
-        <v>8.82</v>
-      </c>
-      <c r="H5" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="I5" t="n">
-        <v>-11245</v>
-      </c>
-      <c r="J5" t="n">
-        <v>15.32</v>
-      </c>
-      <c r="K5" t="n">
-        <v>5.84</v>
-      </c>
-      <c r="L5" t="n">
-        <v>16.18</v>
-      </c>
-      <c r="M5" t="n">
-        <v>3.76</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="O5" t="n">
-        <v>53.41</v>
-      </c>
-      <c r="P5" t="n">
-        <v>28.57142857142857</v>
-      </c>
-      <c r="Q5" t="n">
+      <c r="E5" s="5" t="n">
+        <v>20.07</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>16.61</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="I5" s="5" t="n">
+        <v>10145</v>
+      </c>
+      <c r="J5" s="5" t="n">
+        <v>11.15</v>
+      </c>
+      <c r="K5" s="5" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="L5" s="5" t="n">
+        <v>9.460000000000001</v>
+      </c>
+      <c r="M5" s="5" t="n">
+        <v>57.85</v>
+      </c>
+      <c r="N5" s="5" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="O5" s="5" t="n">
+        <v>75.97</v>
+      </c>
+      <c r="P5" s="3" t="n">
+        <v>57.14285714285714</v>
+      </c>
+      <c r="Q5" s="3" t="n">
+        <v>57.14285714285714</v>
+      </c>
+      <c r="R5" s="2" t="n">
+        <v>85.71428571428571</v>
+      </c>
+      <c r="S5" s="3" t="n">
+        <v>71.42857142857143</v>
+      </c>
+      <c r="T5" s="2" t="n">
+        <v>85.71428571428571</v>
+      </c>
+      <c r="U5" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="R5" t="n">
-        <v>42.85714285714285</v>
-      </c>
-      <c r="S5" t="n">
-        <v>14.28571428571429</v>
-      </c>
-      <c r="T5" t="n">
-        <v>14.28571428571428</v>
-      </c>
-      <c r="U5" t="n">
-        <v>83.33333333333334</v>
-      </c>
-      <c r="V5" t="n">
-        <v>28.57142857142857</v>
-      </c>
-      <c r="W5" t="n">
-        <v>83.33333333333334</v>
-      </c>
-      <c r="X5" t="n">
-        <v>28.57142857142857</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>14.28571428571428</v>
+      <c r="V5" s="3" t="n">
+        <v>71.42857142857143</v>
+      </c>
+      <c r="W5" s="3" t="n">
+        <v>33.33333333333333</v>
+      </c>
+      <c r="X5" s="2" t="n">
+        <v>85.71428571428571</v>
+      </c>
+      <c r="Y5" s="3" t="n">
+        <v>57.14285714285714</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Automobiles</t>
+          <t>ITC</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>MARUTI</t>
+          <t xml:space="preserve">ITC Ltd
+</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -3143,78 +3358,78 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>15.75</v>
+        <v>27.85</v>
       </c>
       <c r="F6" t="n">
-        <v>23.67</v>
+        <v>34.76</v>
       </c>
       <c r="G6" t="n">
-        <v>9.51</v>
+        <v>29.28</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>4936</v>
+        <v>18742</v>
       </c>
       <c r="J6" t="n">
-        <v>12.01</v>
+        <v>10.08</v>
       </c>
       <c r="K6" t="n">
-        <v>10.51</v>
+        <v>7.95</v>
       </c>
       <c r="L6" t="n">
-        <v>11.14</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="M6" t="n">
-        <v>117.91</v>
+        <v>362.96</v>
       </c>
       <c r="N6" t="n">
-        <v>1.23</v>
+        <v>0.77</v>
       </c>
       <c r="O6" t="n">
-        <v>67.33</v>
-      </c>
-      <c r="P6" t="n">
-        <v>14.28571428571428</v>
-      </c>
-      <c r="Q6" t="n">
+        <v>79.56</v>
+      </c>
+      <c r="P6" s="3" t="n">
+        <v>71.42857142857143</v>
+      </c>
+      <c r="Q6" s="3" t="n">
+        <v>71.42857142857143</v>
+      </c>
+      <c r="R6" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="S6" s="2" t="n">
+        <v>85.71428571428572</v>
+      </c>
+      <c r="T6" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="U6" s="3" t="n">
         <v>33.33333333333333</v>
       </c>
-      <c r="R6" t="n">
-        <v>57.14285714285714</v>
-      </c>
-      <c r="S6" t="n">
-        <v>85.71428571428572</v>
-      </c>
-      <c r="T6" t="n">
-        <v>71.42857142857143</v>
-      </c>
-      <c r="U6" t="n">
+      <c r="V6" s="3" t="n">
+        <v>42.85714285714285</v>
+      </c>
+      <c r="W6" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="V6" t="n">
-        <v>71.42857142857143</v>
-      </c>
-      <c r="W6" t="n">
-        <v>50</v>
-      </c>
-      <c r="X6" t="n">
-        <v>85.71428571428571</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>85.71428571428571</v>
+      <c r="X6" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="Y6" s="3" t="n">
+        <v>35.71428571428572</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Automobiles</t>
+          <t>NESTLEIND</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>TATAMOTORS</t>
+          <t>Nestle India Ltd</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -3228,70 +3443,78 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>37.46</v>
+        <v>117.75</v>
       </c>
       <c r="F7" t="n">
-        <v>20.1</v>
+        <v>185.43</v>
       </c>
       <c r="G7" t="n">
-        <v>7.26</v>
+        <v>16.12</v>
       </c>
       <c r="H7" t="n">
-        <v>1.26</v>
+        <v>0.1</v>
       </c>
       <c r="I7" t="n">
-        <v>45133</v>
-      </c>
-      <c r="J7" t="inlineStr"/>
+        <v>2938</v>
+      </c>
+      <c r="J7" t="n">
+        <v>14.85</v>
+      </c>
       <c r="K7" t="n">
-        <v>7.72</v>
-      </c>
-      <c r="L7" t="inlineStr"/>
+        <v>14.55</v>
+      </c>
+      <c r="L7" t="n">
+        <v>15.44</v>
+      </c>
       <c r="M7" t="n">
-        <v>6.53</v>
+        <v>41.19</v>
       </c>
       <c r="N7" t="n">
-        <v>1.19</v>
+        <v>2.32</v>
       </c>
       <c r="O7" t="n">
-        <v>62.94</v>
-      </c>
-      <c r="P7" t="n">
-        <v>100</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>16.66666666666666</v>
-      </c>
-      <c r="R7" t="n">
-        <v>28.57142857142857</v>
-      </c>
-      <c r="S7" t="n">
-        <v>28.57142857142857</v>
-      </c>
-      <c r="T7" t="n">
-        <v>100</v>
-      </c>
-      <c r="U7" t="inlineStr"/>
-      <c r="V7" t="n">
-        <v>42.85714285714285</v>
-      </c>
-      <c r="W7" t="inlineStr"/>
-      <c r="X7" t="n">
-        <v>42.85714285714285</v>
-      </c>
-      <c r="Y7" t="n">
+        <v>84.19</v>
+      </c>
+      <c r="P7" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q7" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="R7" s="3" t="n">
         <v>71.42857142857143</v>
+      </c>
+      <c r="S7" s="3" t="n">
+        <v>57.14285714285715</v>
+      </c>
+      <c r="T7" s="3" t="n">
+        <v>57.14285714285714</v>
+      </c>
+      <c r="U7" s="2" t="n">
+        <v>83.33333333333334</v>
+      </c>
+      <c r="V7" s="2" t="n">
+        <v>85.71428571428571</v>
+      </c>
+      <c r="W7" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="X7" s="3" t="n">
+        <v>71.42857142857143</v>
+      </c>
+      <c r="Y7" s="2" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Automobiles</t>
+          <t>TATACONSUM</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>TVSMOTOR</t>
+          <t>Tata Consumer Products Ltd</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -3305,63 +3528,140 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>26.22</v>
-      </c>
-      <c r="F8" t="inlineStr"/>
+        <v>7.57</v>
+      </c>
+      <c r="F8" t="n">
+        <v>10.6</v>
+      </c>
       <c r="G8" t="n">
-        <v>4.54</v>
+        <v>7.99</v>
       </c>
       <c r="H8" t="n">
-        <v>3.83</v>
+        <v>0.22</v>
       </c>
       <c r="I8" t="n">
-        <v>-2254</v>
+        <v>26</v>
       </c>
       <c r="J8" t="n">
-        <v>19.67</v>
+        <v>21.6</v>
       </c>
       <c r="K8" t="n">
-        <v>14.19</v>
+        <v>15.96</v>
       </c>
       <c r="L8" t="n">
-        <v>19.14</v>
+        <v>14.87</v>
       </c>
       <c r="M8" t="n">
-        <v>2.91</v>
+        <v>25.32</v>
       </c>
       <c r="N8" t="n">
-        <v>0.93</v>
+        <v>0.55</v>
       </c>
       <c r="O8" t="n">
-        <v>50.5</v>
-      </c>
-      <c r="P8" t="n">
-        <v>71.42857142857143</v>
-      </c>
-      <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="n">
+        <v>64.12</v>
+      </c>
+      <c r="P8" s="3" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="Q8" s="4" t="n">
         <v>14.28571428571428</v>
       </c>
-      <c r="S8" t="n">
-        <v>0</v>
-      </c>
-      <c r="T8" t="n">
+      <c r="R8" s="3" t="n">
         <v>28.57142857142857</v>
       </c>
-      <c r="U8" t="n">
-        <v>100</v>
-      </c>
-      <c r="V8" t="n">
-        <v>100</v>
-      </c>
-      <c r="W8" t="n">
-        <v>100</v>
-      </c>
-      <c r="X8" t="n">
+      <c r="S8" s="3" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="T8" s="3" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="U8" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="V8" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="W8" s="2" t="n">
+        <v>83.33333333333334</v>
+      </c>
+      <c r="X8" s="3" t="n">
+        <v>57.14285714285714</v>
+      </c>
+      <c r="Y8" s="4" t="n">
         <v>14.28571428571428</v>
       </c>
-      <c r="Y8" t="n">
-        <v>42.85714285714285</v>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>Median</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="n"/>
+      <c r="C9" s="6" t="n"/>
+      <c r="D9" s="6" t="n"/>
+      <c r="E9" s="6" t="n">
+        <v>20.07</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>2938</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="K9" s="6" t="n">
+        <v>8.69</v>
+      </c>
+      <c r="L9" s="6" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="M9" s="6" t="n">
+        <v>25.32</v>
+      </c>
+      <c r="N9" s="6" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="O9" s="6" t="n">
+        <v>75.97</v>
+      </c>
+      <c r="P9" s="6" t="n">
+        <v>57.14</v>
+      </c>
+      <c r="Q9" s="6" t="n">
+        <v>57.14</v>
+      </c>
+      <c r="R9" s="6" t="n">
+        <v>57.14</v>
+      </c>
+      <c r="S9" s="6" t="n">
+        <v>42.86</v>
+      </c>
+      <c r="T9" s="6" t="n">
+        <v>57.14</v>
+      </c>
+      <c r="U9" s="6" t="n">
+        <v>58.33</v>
+      </c>
+      <c r="V9" s="6" t="n">
+        <v>57.14</v>
+      </c>
+      <c r="W9" s="6" t="n">
+        <v>58.33</v>
+      </c>
+      <c r="X9" s="6" t="n">
+        <v>57.14</v>
+      </c>
+      <c r="Y9" s="6" t="n">
+        <v>57.14</v>
       </c>
     </row>
   </sheetData>
@@ -3375,131 +3675,158 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y4"/>
+  <dimension ref="A1:Y7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="17" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="19" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="20" customWidth="1" min="13" max="13"/>
+    <col width="17" customWidth="1" min="14" max="14"/>
+    <col width="26" customWidth="1" min="15" max="15"/>
+    <col width="34" customWidth="1" min="16" max="16"/>
+    <col width="29" customWidth="1" min="17" max="17"/>
+    <col width="35" customWidth="1" min="18" max="18"/>
+    <col width="28" customWidth="1" min="19" max="19"/>
+    <col width="31" customWidth="1" min="20" max="20"/>
+    <col width="26" customWidth="1" min="21" max="21"/>
+    <col width="30" customWidth="1" min="22" max="22"/>
+    <col width="26" customWidth="1" min="23" max="23"/>
+    <col width="31" customWidth="1" min="24" max="24"/>
+    <col width="28" customWidth="1" min="25" max="25"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>peer_group_name</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>company_id</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>is_benchmark</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>year</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>return_on_equity_pct</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>roce_percentage</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>net_profit_margin_pct</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>debt_to_equity</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>free_cash_flow_cr</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>pat_cagr_5yr</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>revenue_cagr_5yr</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>eps_cagr_5yr</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>interest_coverage</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>asset_turnover</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>composite_quality_score</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>return_on_equity_pct_percentile</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>roce_percentage_percentile</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>net_profit_margin_pct_percentile</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>debt_to_equity_percentile</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>free_cash_flow_cr_percentile</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>pat_cagr_5yr_percentile</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>revenue_cagr_5yr_percentile</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>eps_cagr_5yr_percentile</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>interest_coverage_percentile</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>asset_turnover_percentile</t>
         </is>
@@ -3508,17 +3835,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consumer Finance</t>
+          <t>HCLTECH</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>BAJFINANCE</t>
+          <t>HCL Technologies Ltd</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -3527,78 +3854,78 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>18.84</v>
+        <v>23.01</v>
       </c>
       <c r="F2" t="n">
-        <v>11.9</v>
+        <v>29.6</v>
       </c>
       <c r="G2" t="n">
-        <v>26.29</v>
+        <v>14.29</v>
       </c>
       <c r="H2" t="n">
-        <v>3.82</v>
+        <v>0.08</v>
       </c>
       <c r="I2" t="n">
-        <v>-79931</v>
+        <v>15840</v>
       </c>
       <c r="J2" t="n">
-        <v>29.32</v>
+        <v>9.19</v>
       </c>
       <c r="K2" t="n">
-        <v>24.35</v>
+        <v>12.71</v>
       </c>
       <c r="L2" t="n">
-        <v>27.56</v>
+        <v>9.41</v>
       </c>
       <c r="M2" t="n">
-        <v>2689.17</v>
+        <v>46.46</v>
       </c>
       <c r="N2" t="n">
-        <v>0.15</v>
+        <v>1.11</v>
       </c>
       <c r="O2" t="n">
-        <v>57.47</v>
-      </c>
-      <c r="P2" t="n">
-        <v>100</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>100</v>
-      </c>
-      <c r="R2" t="n">
-        <v>100</v>
-      </c>
-      <c r="S2" t="n">
-        <v>66.66666666666667</v>
-      </c>
-      <c r="T2" t="n">
-        <v>33.33333333333333</v>
-      </c>
-      <c r="U2" t="n">
-        <v>100</v>
-      </c>
-      <c r="V2" t="n">
-        <v>100</v>
-      </c>
-      <c r="W2" t="n">
-        <v>100</v>
-      </c>
-      <c r="X2" t="n">
-        <v>100</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>83.33333333333334</v>
+        <v>80.11</v>
+      </c>
+      <c r="P2" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="Q2" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="S2" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="T2" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="U2" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="V2" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="W2" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="X2" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="Y2" s="4" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Consumer Finance</t>
+          <t>INFY</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CHOLAFIN</t>
+          <t>Infosys Ltd</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -3612,78 +3939,78 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>17.46</v>
+        <v>29.79</v>
       </c>
       <c r="F3" t="n">
-        <v>10.4</v>
+        <v>40</v>
       </c>
       <c r="G3" t="n">
-        <v>17.85</v>
+        <v>17.08</v>
       </c>
       <c r="H3" t="n">
-        <v>6.86</v>
+        <v>0.09</v>
       </c>
       <c r="I3" t="n">
-        <v>-38538</v>
+        <v>20117</v>
       </c>
       <c r="J3" t="n">
-        <v>23.36</v>
+        <v>11.24</v>
       </c>
       <c r="K3" t="n">
-        <v>21.94</v>
+        <v>13.2</v>
       </c>
       <c r="L3" t="n">
-        <v>22.28</v>
+        <v>12.47</v>
       </c>
       <c r="M3" t="n">
-        <v>21.21</v>
+        <v>87.52</v>
       </c>
       <c r="N3" t="n">
-        <v>0.12</v>
+        <v>1.13</v>
       </c>
       <c r="O3" t="n">
-        <v>48.86</v>
-      </c>
-      <c r="P3" t="n">
-        <v>66.66666666666666</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>33.33333333333333</v>
-      </c>
-      <c r="R3" t="n">
-        <v>33.33333333333333</v>
-      </c>
-      <c r="S3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T3" t="n">
-        <v>66.66666666666666</v>
-      </c>
-      <c r="U3" t="n">
-        <v>33.33333333333333</v>
-      </c>
-      <c r="V3" t="n">
-        <v>66.66666666666666</v>
-      </c>
-      <c r="W3" t="n">
-        <v>66.66666666666666</v>
-      </c>
-      <c r="X3" t="n">
-        <v>66.66666666666666</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>33.33333333333333</v>
+        <v>83.59</v>
+      </c>
+      <c r="P3" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="Q3" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="R3" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="S3" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="T3" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="U3" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="V3" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="W3" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="X3" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="Y3" s="3" t="n">
+        <v>40</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Consumer Finance</t>
+          <t>LTIM</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>SHRIRAMFIN</t>
+          <t>LTIMindtree Ltd</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -3697,67 +4024,310 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>15.12</v>
+        <v>22.9</v>
       </c>
       <c r="F4" t="n">
-        <v>11.3</v>
+        <v>34.1</v>
       </c>
       <c r="G4" t="n">
-        <v>20.33</v>
+        <v>12.91</v>
       </c>
       <c r="H4" t="n">
-        <v>3.99</v>
+        <v>0.1</v>
       </c>
       <c r="I4" t="n">
-        <v>-31359</v>
+        <v>1752</v>
       </c>
       <c r="J4" t="n">
-        <v>23.49</v>
+        <v>24.78</v>
       </c>
       <c r="K4" t="n">
-        <v>18.56</v>
+        <v>30.33</v>
       </c>
       <c r="L4" t="n">
+        <v>12.24</v>
+      </c>
+      <c r="M4" t="n">
+        <v>31.93</v>
+      </c>
+      <c r="N4" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="O4" t="n">
+        <v>72.55</v>
+      </c>
+      <c r="P4" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="Q4" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="S4" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="U4" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="V4" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="W4" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="X4" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="Y4" s="2" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>TCS</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Tata Consultancy Services Ltd</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>Mar 2024</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>50.94</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>64.3</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>19.14</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="I5" s="5" t="n">
+        <v>50429</v>
+      </c>
+      <c r="J5" s="5" t="n">
+        <v>7.87</v>
+      </c>
+      <c r="K5" s="5" t="n">
+        <v>10.46</v>
+      </c>
+      <c r="L5" s="5" t="n">
+        <v>8.619999999999999</v>
+      </c>
+      <c r="M5" s="5" t="n">
+        <v>87.09999999999999</v>
+      </c>
+      <c r="N5" s="5" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="O5" s="5" t="n">
+        <v>85.89</v>
+      </c>
+      <c r="P5" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q5" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="R5" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="S5" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="T5" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="U5" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="V5" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="W5" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="X5" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="Y5" s="2" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>TECHM</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Tech Mahindra Ltd</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Mar 2024</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>8.99</v>
+      </c>
+      <c r="F6" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="G6" t="n">
+        <v>4.61</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I6" t="n">
+        <v>5058</v>
+      </c>
+      <c r="J6" t="n">
+        <v>-10.99</v>
+      </c>
+      <c r="K6" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="L6" t="n">
+        <v>-11.42</v>
+      </c>
+      <c r="M6" t="n">
+        <v>13.86</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="O6" t="n">
+        <v>64.93000000000001</v>
+      </c>
+      <c r="P6" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q6" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="R6" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="S6" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="U6" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="V6" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="W6" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="X6" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y6" s="3" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Median</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n"/>
+      <c r="C7" s="6" t="n"/>
+      <c r="D7" s="6" t="n"/>
+      <c r="E7" s="6" t="n">
+        <v>23.01</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>34.1</v>
+      </c>
+      <c r="G7" s="6" t="n">
         <v>14.29</v>
       </c>
-      <c r="M4" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="O4" t="n">
-        <v>53.19</v>
-      </c>
-      <c r="P4" t="n">
-        <v>33.33333333333333</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>66.66666666666666</v>
-      </c>
-      <c r="R4" t="n">
-        <v>66.66666666666666</v>
-      </c>
-      <c r="S4" t="n">
-        <v>33.33333333333334</v>
-      </c>
-      <c r="T4" t="n">
-        <v>100</v>
-      </c>
-      <c r="U4" t="n">
-        <v>66.66666666666666</v>
-      </c>
-      <c r="V4" t="n">
-        <v>33.33333333333333</v>
-      </c>
-      <c r="W4" t="n">
-        <v>33.33333333333333</v>
-      </c>
-      <c r="X4" t="n">
-        <v>33.33333333333333</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>83.33333333333334</v>
+      <c r="H7" s="6" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>15840</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>9.19</v>
+      </c>
+      <c r="K7" s="6" t="n">
+        <v>12.71</v>
+      </c>
+      <c r="L7" s="6" t="n">
+        <v>9.41</v>
+      </c>
+      <c r="M7" s="6" t="n">
+        <v>46.46</v>
+      </c>
+      <c r="N7" s="6" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="O7" s="6" t="n">
+        <v>80.11</v>
+      </c>
+      <c r="P7" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="Q7" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="R7" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="S7" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="T7" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="U7" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="V7" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="W7" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="X7" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="Y7" s="6" t="n">
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -3771,131 +4341,158 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y4"/>
+  <dimension ref="A1:Y6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="46" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="17" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="19" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="20" customWidth="1" min="13" max="13"/>
+    <col width="17" customWidth="1" min="14" max="14"/>
+    <col width="26" customWidth="1" min="15" max="15"/>
+    <col width="34" customWidth="1" min="16" max="16"/>
+    <col width="29" customWidth="1" min="17" max="17"/>
+    <col width="35" customWidth="1" min="18" max="18"/>
+    <col width="28" customWidth="1" min="19" max="19"/>
+    <col width="31" customWidth="1" min="20" max="20"/>
+    <col width="26" customWidth="1" min="21" max="21"/>
+    <col width="30" customWidth="1" min="22" max="22"/>
+    <col width="26" customWidth="1" min="23" max="23"/>
+    <col width="31" customWidth="1" min="24" max="24"/>
+    <col width="28" customWidth="1" min="25" max="25"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>peer_group_name</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>company_id</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>is_benchmark</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>year</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>return_on_equity_pct</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>roce_percentage</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>net_profit_margin_pct</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>debt_to_equity</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>free_cash_flow_cr</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>pat_cagr_5yr</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>revenue_cagr_5yr</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>eps_cagr_5yr</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>interest_coverage</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>asset_turnover</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>composite_quality_score</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>return_on_equity_pct_percentile</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>roce_percentage_percentile</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>net_profit_margin_pct_percentile</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>debt_to_equity_percentile</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>free_cash_flow_cr_percentile</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>pat_cagr_5yr_percentile</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>revenue_cagr_5yr_percentile</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>eps_cagr_5yr_percentile</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>interest_coverage_percentile</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>asset_turnover_percentile</t>
         </is>
@@ -3904,12 +4501,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Public Sector Banks</t>
+          <t>HDFCLIFE</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>BANKBARODA</t>
+          <t>HDFC Life Insurance Company Ltd</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -3923,78 +4520,78 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>15.76</v>
+        <v>10.73</v>
       </c>
       <c r="F2" t="n">
-        <v>6.33</v>
+        <v>6.61</v>
       </c>
       <c r="G2" t="n">
-        <v>15.94</v>
+        <v>1.55</v>
       </c>
       <c r="H2" t="n">
-        <v>12.14</v>
+        <v>0.06</v>
       </c>
       <c r="I2" t="n">
-        <v>-7559</v>
+        <v>-2893</v>
       </c>
       <c r="J2" t="n">
-        <v>74.51000000000001</v>
+        <v>4.25</v>
       </c>
       <c r="K2" t="n">
-        <v>17.48</v>
+        <v>21.17</v>
       </c>
       <c r="L2" t="n">
-        <v>55.18</v>
+        <v>3.13</v>
       </c>
       <c r="M2" t="n">
-        <v>1.9</v>
+        <v>192.29</v>
       </c>
       <c r="N2" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.34</v>
       </c>
       <c r="O2" t="n">
-        <v>49.07</v>
-      </c>
-      <c r="P2" t="n">
-        <v>33.33333333333333</v>
-      </c>
-      <c r="Q2" t="n">
+        <v>69.42</v>
+      </c>
+      <c r="P2" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q2" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="R2" s="2" t="n">
+        <v>75</v>
+      </c>
+      <c r="S2" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T2" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="U2" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="V2" s="2" t="n">
+        <v>75</v>
+      </c>
+      <c r="W2" s="3" t="n">
         <v>66.66666666666666</v>
       </c>
-      <c r="R2" t="n">
-        <v>100</v>
-      </c>
-      <c r="S2" t="n">
-        <v>33.33333333333334</v>
-      </c>
-      <c r="T2" t="n">
-        <v>66.66666666666666</v>
-      </c>
-      <c r="U2" t="n">
+      <c r="X2" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="V2" t="n">
-        <v>66.66666666666666</v>
-      </c>
-      <c r="W2" t="n">
-        <v>100</v>
-      </c>
-      <c r="X2" t="n">
-        <v>100</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>50</v>
+      <c r="Y2" s="2" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Public Sector Banks</t>
+          <t>ICICIPRULI</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CANBK</t>
+          <t>ICICI Prudential Life Insurance Company Ltd</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -4008,144 +4605,306 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>16.72</v>
+        <v>7.73</v>
       </c>
       <c r="F3" t="n">
-        <v>6.63</v>
+        <v>8.75</v>
       </c>
       <c r="G3" t="n">
-        <v>13.94</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H3" t="n">
-        <v>14.87</v>
+        <v>0.11</v>
       </c>
       <c r="I3" t="n">
-        <v>13296</v>
+        <v>105</v>
       </c>
       <c r="J3" t="n">
-        <v>85.78</v>
+        <v>-5.66</v>
       </c>
       <c r="K3" t="n">
-        <v>18.18</v>
+        <v>16.85</v>
       </c>
       <c r="L3" t="n">
-        <v>53.42</v>
+        <v>-5.59</v>
       </c>
       <c r="M3" t="n">
-        <v>1.61</v>
+        <v>31.02</v>
       </c>
       <c r="N3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.3</v>
       </c>
       <c r="O3" t="n">
-        <v>59.34</v>
-      </c>
-      <c r="P3" t="n">
-        <v>66.66666666666666</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>100</v>
-      </c>
-      <c r="R3" t="n">
-        <v>66.66666666666666</v>
-      </c>
-      <c r="S3" t="n">
+        <v>65.22</v>
+      </c>
+      <c r="P3" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q3" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="R3" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="S3" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="T3" t="n">
-        <v>100</v>
-      </c>
-      <c r="U3" t="n">
-        <v>100</v>
-      </c>
-      <c r="V3" t="n">
-        <v>100</v>
-      </c>
-      <c r="W3" t="n">
+      <c r="T3" s="2" t="n">
+        <v>75</v>
+      </c>
+      <c r="U3" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="V3" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="X3" t="n">
-        <v>66.66666666666666</v>
-      </c>
-      <c r="Y3" t="n">
+      <c r="W3" s="3" t="n">
+        <v>33.33333333333333</v>
+      </c>
+      <c r="X3" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y3" s="3" t="n">
         <v>50</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Public Sector Banks</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>PNB</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>LICI</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>Life Insurance Corporation of India</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>Mar 2024</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>49.45</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>63.79</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>4.84</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" s="5" t="n">
+        <v>853</v>
+      </c>
+      <c r="J4" s="5" t="n">
+        <v>73.18000000000001</v>
+      </c>
+      <c r="K4" s="5" t="n">
+        <v>8.16</v>
+      </c>
+      <c r="L4" s="5" t="inlineStr"/>
+      <c r="M4" s="5" t="n">
+        <v>371.94</v>
+      </c>
+      <c r="N4" s="5" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="O4" s="5" t="n">
+        <v>69.53</v>
+      </c>
+      <c r="P4" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q4" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="R4" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="S4" s="3" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="T4" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="U4" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="V4" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="W4" s="5" t="inlineStr"/>
+      <c r="X4" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="Y4" s="4" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>SBILIFE</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>SBI Life Insurance Company Ltd</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>Mar 2024</t>
         </is>
       </c>
-      <c r="E4" t="n">
-        <v>61.32</v>
-      </c>
-      <c r="F4" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="G4" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="H4" t="n">
-        <v>3.68</v>
-      </c>
-      <c r="I4" t="n">
-        <v>-29445</v>
-      </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="N4" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="O4" t="n">
-        <v>64.92</v>
-      </c>
-      <c r="P4" t="n">
-        <v>100</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>33.33333333333333</v>
-      </c>
-      <c r="R4" t="n">
-        <v>33.33333333333333</v>
-      </c>
-      <c r="S4" t="n">
-        <v>66.66666666666667</v>
-      </c>
-      <c r="T4" t="n">
-        <v>33.33333333333333</v>
-      </c>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="n">
-        <v>33.33333333333333</v>
-      </c>
-      <c r="W4" t="inlineStr"/>
-      <c r="X4" t="n">
-        <v>33.33333333333333</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>100</v>
+      <c r="E5" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="F5" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>-2099</v>
+      </c>
+      <c r="J5" t="n">
+        <v>7.37</v>
+      </c>
+      <c r="K5" t="n">
+        <v>24.23</v>
+      </c>
+      <c r="L5" t="n">
+        <v>7.89</v>
+      </c>
+      <c r="M5" t="n">
+        <v>240.33</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="O5" t="n">
+        <v>55.2</v>
+      </c>
+      <c r="P5" s="2" t="n">
+        <v>75</v>
+      </c>
+      <c r="Q5" s="2" t="n">
+        <v>75</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="S5" s="3" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="T5" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="U5" s="2" t="n">
+        <v>75</v>
+      </c>
+      <c r="V5" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="W5" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="X5" s="2" t="n">
+        <v>75</v>
+      </c>
+      <c r="Y5" s="2" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Median</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n"/>
+      <c r="C6" s="6" t="n"/>
+      <c r="D6" s="6" t="n"/>
+      <c r="E6" s="6" t="n">
+        <v>11.72</v>
+      </c>
+      <c r="F6" s="6" t="n">
+        <v>10.98</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>-997</v>
+      </c>
+      <c r="J6" s="6" t="n">
+        <v>5.81</v>
+      </c>
+      <c r="K6" s="6" t="n">
+        <v>19.01</v>
+      </c>
+      <c r="L6" s="6" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="M6" s="6" t="n">
+        <v>216.31</v>
+      </c>
+      <c r="N6" s="6" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="O6" s="6" t="n">
+        <v>67.31999999999999</v>
+      </c>
+      <c r="P6" s="6" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="Q6" s="6" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="R6" s="6" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="S6" s="6" t="n">
+        <v>43.75</v>
+      </c>
+      <c r="T6" s="6" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="U6" s="6" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="V6" s="6" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="W6" s="6" t="n">
+        <v>66.67</v>
+      </c>
+      <c r="X6" s="6" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="Y6" s="6" t="n">
+        <v>62.5</v>
       </c>
     </row>
   </sheetData>
@@ -4159,131 +4918,158 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y6"/>
+  <dimension ref="A1:Y7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="35" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="17" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="19" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="20" customWidth="1" min="13" max="13"/>
+    <col width="17" customWidth="1" min="14" max="14"/>
+    <col width="26" customWidth="1" min="15" max="15"/>
+    <col width="34" customWidth="1" min="16" max="16"/>
+    <col width="29" customWidth="1" min="17" max="17"/>
+    <col width="35" customWidth="1" min="18" max="18"/>
+    <col width="28" customWidth="1" min="19" max="19"/>
+    <col width="31" customWidth="1" min="20" max="20"/>
+    <col width="26" customWidth="1" min="21" max="21"/>
+    <col width="30" customWidth="1" min="22" max="22"/>
+    <col width="26" customWidth="1" min="23" max="23"/>
+    <col width="31" customWidth="1" min="24" max="24"/>
+    <col width="28" customWidth="1" min="25" max="25"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>peer_group_name</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>company_id</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>is_benchmark</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>year</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>return_on_equity_pct</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>roce_percentage</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>net_profit_margin_pct</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>debt_to_equity</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>free_cash_flow_cr</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>pat_cagr_5yr</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>revenue_cagr_5yr</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>eps_cagr_5yr</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>interest_coverage</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>asset_turnover</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>composite_quality_score</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>return_on_equity_pct_percentile</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>roce_percentage_percentile</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>net_profit_margin_pct_percentile</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>debt_to_equity_percentile</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>free_cash_flow_cr_percentile</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>pat_cagr_5yr_percentile</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>revenue_cagr_5yr_percentile</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>eps_cagr_5yr_percentile</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>interest_coverage_percentile</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>asset_turnover_percentile</t>
         </is>
@@ -4292,12 +5078,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Oil &amp; Gas</t>
+          <t>BPCL</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>BPCL</t>
+          <t>Bharat Petroleum Corporation Ltd</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -4343,46 +5129,46 @@
       <c r="O2" t="n">
         <v>76.27</v>
       </c>
-      <c r="P2" t="n">
-        <v>100</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>100</v>
-      </c>
-      <c r="R2" t="n">
+      <c r="P2" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q2" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="R2" s="3" t="n">
         <v>40</v>
       </c>
-      <c r="S2" t="n">
+      <c r="S2" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="T2" t="n">
+      <c r="T2" s="3" t="n">
         <v>40</v>
       </c>
-      <c r="U2" t="n">
-        <v>100</v>
-      </c>
-      <c r="V2" t="n">
+      <c r="U2" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="V2" s="3" t="n">
         <v>60</v>
       </c>
-      <c r="W2" t="n">
-        <v>100</v>
-      </c>
-      <c r="X2" t="n">
+      <c r="W2" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="X2" s="3" t="n">
         <v>70</v>
       </c>
-      <c r="Y2" t="n">
+      <c r="Y2" s="2" t="n">
         <v>100</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Oil &amp; Gas</t>
+          <t>GAIL</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>GAIL</t>
+          <t>GAIL (India) Ltd</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -4428,46 +5214,47 @@
       <c r="O3" t="n">
         <v>58.68</v>
       </c>
-      <c r="P3" t="n">
+      <c r="P3" s="3" t="n">
         <v>40</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="Q3" s="3" t="n">
         <v>40</v>
       </c>
-      <c r="R3" t="n">
+      <c r="R3" s="3" t="n">
         <v>60</v>
       </c>
-      <c r="S3" t="n">
+      <c r="S3" s="2" t="n">
         <v>80</v>
       </c>
-      <c r="T3" t="n">
+      <c r="T3" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="U3" t="n">
+      <c r="U3" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="V3" t="n">
-        <v>100</v>
-      </c>
-      <c r="W3" t="n">
+      <c r="V3" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="W3" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="X3" t="n">
-        <v>100</v>
-      </c>
-      <c r="Y3" t="n">
+      <c r="X3" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="Y3" s="3" t="n">
         <v>60</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Oil &amp; Gas</t>
+          <t>IOC</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>IOC</t>
+          <t xml:space="preserve">Indian Oil Corporation
+</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -4513,46 +5300,46 @@
       <c r="O4" t="n">
         <v>71.18000000000001</v>
       </c>
-      <c r="P4" t="n">
+      <c r="P4" s="2" t="n">
         <v>80</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="Q4" s="2" t="n">
         <v>80</v>
       </c>
-      <c r="R4" t="n">
+      <c r="R4" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="S4" t="n">
+      <c r="S4" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="T4" t="n">
+      <c r="T4" s="3" t="n">
         <v>60</v>
       </c>
-      <c r="U4" t="n">
+      <c r="U4" s="2" t="n">
         <v>80</v>
       </c>
-      <c r="V4" t="n">
+      <c r="V4" s="3" t="n">
         <v>40</v>
       </c>
-      <c r="W4" t="n">
+      <c r="W4" s="2" t="n">
         <v>80</v>
       </c>
-      <c r="X4" t="n">
+      <c r="X4" s="3" t="n">
         <v>40</v>
       </c>
-      <c r="Y4" t="n">
+      <c r="Y4" s="2" t="n">
         <v>80</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Oil &amp; Gas</t>
+          <t>ONGC</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ONGC</t>
+          <t>Oil &amp; Natural Gas Corpn Ltd</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -4598,120 +5385,194 @@
       <c r="O5" t="n">
         <v>70.45999999999999</v>
       </c>
-      <c r="P5" t="n">
+      <c r="P5" s="3" t="n">
         <v>60</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="Q5" s="3" t="n">
         <v>60</v>
       </c>
-      <c r="R5" t="n">
-        <v>100</v>
-      </c>
-      <c r="S5" t="n">
+      <c r="R5" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="S5" s="3" t="n">
         <v>60</v>
       </c>
-      <c r="T5" t="n">
+      <c r="T5" s="2" t="n">
         <v>80</v>
       </c>
-      <c r="U5" t="n">
+      <c r="U5" s="3" t="n">
         <v>40</v>
       </c>
-      <c r="V5" t="n">
+      <c r="V5" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="W5" t="n">
+      <c r="W5" s="3" t="n">
         <v>40</v>
       </c>
-      <c r="X5" t="n">
+      <c r="X5" s="3" t="n">
         <v>70</v>
       </c>
-      <c r="Y5" t="n">
+      <c r="Y5" s="3" t="n">
         <v>40</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Oil &amp; Gas</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>RELIANCE</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reliance Industries Ltd
+</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>Mar 2024</t>
         </is>
       </c>
-      <c r="E6" t="n">
+      <c r="E6" s="5" t="n">
         <v>9.960000000000001</v>
       </c>
-      <c r="F6" t="n">
+      <c r="F6" s="5" t="n">
         <v>9.609999999999999</v>
       </c>
-      <c r="G6" t="n">
+      <c r="G6" s="5" t="n">
         <v>8.789999999999999</v>
       </c>
-      <c r="H6" t="n">
+      <c r="H6" s="5" t="n">
         <v>0.58</v>
       </c>
-      <c r="I6" t="n">
+      <c r="I6" s="5" t="n">
         <v>45207</v>
       </c>
-      <c r="J6" t="n">
+      <c r="J6" s="5" t="n">
         <v>14.68</v>
       </c>
-      <c r="K6" t="n">
+      <c r="K6" s="5" t="n">
         <v>9.609999999999999</v>
       </c>
-      <c r="L6" t="n">
+      <c r="L6" s="5" t="n">
         <v>11.95</v>
       </c>
-      <c r="M6" t="n">
+      <c r="M6" s="5" t="n">
         <v>7.73</v>
       </c>
-      <c r="N6" t="n">
+      <c r="N6" s="5" t="n">
         <v>0.51</v>
       </c>
-      <c r="O6" t="n">
+      <c r="O6" s="5" t="n">
         <v>67.22</v>
       </c>
-      <c r="P6" t="n">
+      <c r="P6" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="Q6" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="R6" t="n">
+      <c r="R6" s="2" t="n">
         <v>80</v>
       </c>
-      <c r="S6" t="n">
+      <c r="S6" s="3" t="n">
         <v>40</v>
       </c>
-      <c r="T6" t="n">
-        <v>100</v>
-      </c>
-      <c r="U6" t="n">
+      <c r="T6" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="U6" s="3" t="n">
         <v>60</v>
       </c>
-      <c r="V6" t="n">
+      <c r="V6" s="2" t="n">
         <v>80</v>
       </c>
-      <c r="W6" t="n">
+      <c r="W6" s="3" t="n">
         <v>60</v>
       </c>
-      <c r="X6" t="n">
+      <c r="X6" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="Y6" t="n">
+      <c r="Y6" s="4" t="n">
         <v>20</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Median</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n"/>
+      <c r="C7" s="6" t="n"/>
+      <c r="D7" s="6" t="n"/>
+      <c r="E7" s="6" t="n">
+        <v>16.94</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>19.71</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>7.43</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>39635</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>14.68</v>
+      </c>
+      <c r="K7" s="6" t="n">
+        <v>8.48</v>
+      </c>
+      <c r="L7" s="6" t="n">
+        <v>11.95</v>
+      </c>
+      <c r="M7" s="6" t="n">
+        <v>11.36</v>
+      </c>
+      <c r="N7" s="6" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="O7" s="6" t="n">
+        <v>70.45999999999999</v>
+      </c>
+      <c r="P7" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="Q7" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="R7" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="S7" s="6" t="n">
+        <v>40</v>
+      </c>
+      <c r="T7" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="U7" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="V7" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="W7" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="X7" s="6" t="n">
+        <v>70</v>
+      </c>
+      <c r="Y7" s="6" t="n">
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -4725,131 +5586,158 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y8"/>
+  <dimension ref="A1:Y7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="37" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="17" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="19" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="20" customWidth="1" min="13" max="13"/>
+    <col width="17" customWidth="1" min="14" max="14"/>
+    <col width="26" customWidth="1" min="15" max="15"/>
+    <col width="34" customWidth="1" min="16" max="16"/>
+    <col width="29" customWidth="1" min="17" max="17"/>
+    <col width="35" customWidth="1" min="18" max="18"/>
+    <col width="28" customWidth="1" min="19" max="19"/>
+    <col width="31" customWidth="1" min="20" max="20"/>
+    <col width="26" customWidth="1" min="21" max="21"/>
+    <col width="30" customWidth="1" min="22" max="22"/>
+    <col width="26" customWidth="1" min="23" max="23"/>
+    <col width="31" customWidth="1" min="24" max="24"/>
+    <col width="28" customWidth="1" min="25" max="25"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>peer_group_name</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>company_id</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>is_benchmark</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>year</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>return_on_equity_pct</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>roce_percentage</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>net_profit_margin_pct</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>debt_to_equity</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>free_cash_flow_cr</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>pat_cagr_5yr</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>revenue_cagr_5yr</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>eps_cagr_5yr</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>interest_coverage</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>asset_turnover</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>composite_quality_score</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>return_on_equity_pct_percentile</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>roce_percentage_percentile</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>net_profit_margin_pct_percentile</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>debt_to_equity_percentile</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>free_cash_flow_cr_percentile</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>pat_cagr_5yr_percentile</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>revenue_cagr_5yr_percentile</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>eps_cagr_5yr_percentile</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>interest_coverage_percentile</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>asset_turnover_percentile</t>
         </is>
@@ -4858,12 +5746,13 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>CIPLA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>BRITANNIA</t>
+          <t xml:space="preserve">Cipla Ltd
+</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -4877,78 +5766,78 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>54.15</v>
+        <v>15.55</v>
       </c>
       <c r="F2" t="n">
-        <v>48.9</v>
+        <v>22.8</v>
       </c>
       <c r="G2" t="n">
-        <v>12.73</v>
+        <v>16.12</v>
       </c>
       <c r="H2" t="n">
-        <v>0.52</v>
+        <v>0.02</v>
       </c>
       <c r="I2" t="n">
-        <v>3050</v>
+        <v>1152</v>
       </c>
       <c r="J2" t="n">
-        <v>13.06</v>
+        <v>22.73</v>
       </c>
       <c r="K2" t="n">
-        <v>8.69</v>
+        <v>9.51</v>
       </c>
       <c r="L2" t="n">
-        <v>13.14</v>
+        <v>21.83</v>
       </c>
       <c r="M2" t="n">
-        <v>20.6</v>
+        <v>35.34</v>
       </c>
       <c r="N2" t="n">
-        <v>1.85</v>
+        <v>0.79</v>
       </c>
       <c r="O2" t="n">
-        <v>83.70999999999999</v>
-      </c>
-      <c r="P2" t="n">
-        <v>85.71428571428571</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>85.71428571428571</v>
-      </c>
-      <c r="R2" t="n">
-        <v>42.85714285714285</v>
-      </c>
-      <c r="S2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T2" t="n">
-        <v>71.42857142857143</v>
-      </c>
-      <c r="U2" t="n">
-        <v>66.66666666666666</v>
-      </c>
-      <c r="V2" t="n">
-        <v>57.14285714285714</v>
-      </c>
-      <c r="W2" t="n">
-        <v>66.66666666666666</v>
-      </c>
-      <c r="X2" t="n">
-        <v>28.57142857142857</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>85.71428571428571</v>
+        <v>75.34</v>
+      </c>
+      <c r="P2" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="Q2" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="S2" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="T2" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="U2" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="V2" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="W2" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="X2" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="Y2" s="2" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>DIVISLAB</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>DABUR</t>
+          <t>Divis Laboratories Ltd</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -4962,78 +5851,78 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>18.36</v>
+        <v>11.79</v>
       </c>
       <c r="F3" t="n">
-        <v>22.3</v>
+        <v>16.5</v>
       </c>
       <c r="G3" t="n">
-        <v>14.6</v>
+        <v>20.4</v>
       </c>
       <c r="H3" t="n">
-        <v>0.14</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>1042</v>
+        <v>992</v>
       </c>
       <c r="J3" t="n">
-        <v>4.6</v>
+        <v>3.41</v>
       </c>
       <c r="K3" t="n">
-        <v>7.81</v>
+        <v>9.66</v>
       </c>
       <c r="L3" t="n">
-        <v>4.56</v>
+        <v>3.3</v>
       </c>
       <c r="M3" t="n">
-        <v>23.24</v>
+        <v>636.25</v>
       </c>
       <c r="N3" t="n">
-        <v>0.82</v>
+        <v>0.51</v>
       </c>
       <c r="O3" t="n">
-        <v>72.03</v>
-      </c>
-      <c r="P3" t="n">
-        <v>42.85714285714285</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>28.57142857142857</v>
-      </c>
-      <c r="R3" t="n">
-        <v>57.14285714285714</v>
-      </c>
-      <c r="S3" t="n">
-        <v>42.85714285714286</v>
-      </c>
-      <c r="T3" t="n">
-        <v>42.85714285714285</v>
-      </c>
-      <c r="U3" t="n">
-        <v>16.66666666666666</v>
-      </c>
-      <c r="V3" t="n">
-        <v>28.57142857142857</v>
-      </c>
-      <c r="W3" t="n">
-        <v>16.66666666666666</v>
-      </c>
-      <c r="X3" t="n">
-        <v>42.85714285714285</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>71.42857142857143</v>
+        <v>68.5</v>
+      </c>
+      <c r="P3" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q3" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="R3" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="S3" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="T3" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="U3" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="V3" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="W3" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="X3" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="Y3" s="4" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>DRREDDY</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>GODREJCP</t>
+          <t>Dr Reddys Laboratories Ltd</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -5047,155 +5936,163 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>-4.45</v>
+        <v>19.74</v>
       </c>
       <c r="F4" t="n">
-        <v>26.49</v>
+        <v>26.5</v>
       </c>
       <c r="G4" t="n">
-        <v>-3.98</v>
+        <v>19.91</v>
       </c>
       <c r="H4" t="n">
-        <v>0.26</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>-1365</v>
-      </c>
-      <c r="J4" t="inlineStr"/>
+        <v>509</v>
+      </c>
+      <c r="J4" t="n">
+        <v>23.39</v>
+      </c>
       <c r="K4" t="n">
-        <v>6.45</v>
-      </c>
-      <c r="L4" t="inlineStr"/>
+        <v>12.64</v>
+      </c>
+      <c r="L4" t="n">
+        <v>23.84</v>
+      </c>
       <c r="M4" t="n">
-        <v>2.41</v>
+        <v>51.71</v>
       </c>
       <c r="N4" t="n">
-        <v>0.77</v>
+        <v>0.72</v>
       </c>
       <c r="O4" t="n">
-        <v>58.78</v>
-      </c>
-      <c r="P4" t="n">
-        <v>14.28571428571428</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>42.85714285714285</v>
-      </c>
-      <c r="R4" t="n">
-        <v>14.28571428571428</v>
-      </c>
-      <c r="S4" t="n">
-        <v>14.28571428571429</v>
-      </c>
-      <c r="T4" t="n">
-        <v>14.28571428571428</v>
-      </c>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="n">
-        <v>14.28571428571428</v>
-      </c>
-      <c r="W4" t="inlineStr"/>
-      <c r="X4" t="n">
-        <v>14.28571428571428</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>35.71428571428572</v>
+        <v>77.73</v>
+      </c>
+      <c r="P4" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="Q4" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="R4" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="S4" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="T4" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="U4" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="V4" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="W4" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="X4" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="Y4" s="3" t="n">
+        <v>60</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>FMCG</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>HINDUNILVR</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>SUNPHARMA</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Sun Pharmaceuticals Industries Ltd</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>Mar 2024</t>
         </is>
       </c>
-      <c r="E5" t="n">
-        <v>20.07</v>
-      </c>
-      <c r="F5" t="n">
-        <v>27.2</v>
-      </c>
-      <c r="G5" t="n">
-        <v>16.61</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="I5" t="n">
-        <v>10145</v>
-      </c>
-      <c r="J5" t="n">
-        <v>11.15</v>
-      </c>
-      <c r="K5" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="L5" t="n">
-        <v>9.460000000000001</v>
-      </c>
-      <c r="M5" t="n">
-        <v>57.85</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0.79</v>
-      </c>
-      <c r="O5" t="n">
-        <v>75.97</v>
-      </c>
-      <c r="P5" t="n">
-        <v>57.14285714285714</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>57.14285714285714</v>
-      </c>
-      <c r="R5" t="n">
-        <v>85.71428571428571</v>
-      </c>
-      <c r="S5" t="n">
-        <v>71.42857142857143</v>
-      </c>
-      <c r="T5" t="n">
-        <v>85.71428571428571</v>
-      </c>
-      <c r="U5" t="n">
-        <v>50</v>
-      </c>
-      <c r="V5" t="n">
-        <v>71.42857142857143</v>
-      </c>
-      <c r="W5" t="n">
-        <v>33.33333333333333</v>
-      </c>
-      <c r="X5" t="n">
-        <v>85.71428571428571</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>57.14285714285714</v>
+      <c r="E5" s="5" t="n">
+        <v>15.09</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>19.82</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="I5" s="5" t="n">
+        <v>11372</v>
+      </c>
+      <c r="J5" s="5" t="n">
+        <v>24.54</v>
+      </c>
+      <c r="K5" s="5" t="n">
+        <v>10.78</v>
+      </c>
+      <c r="L5" s="5" t="n">
+        <v>29.46</v>
+      </c>
+      <c r="M5" s="5" t="n">
+        <v>58.33</v>
+      </c>
+      <c r="N5" s="5" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="O5" s="5" t="n">
+        <v>85.44</v>
+      </c>
+      <c r="P5" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="Q5" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="S5" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="T5" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="U5" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="V5" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="W5" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="X5" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="Y5" s="3" t="n">
+        <v>40</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>TORNTPHARM</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ITC</t>
+          <t>Torrent Pharmaceuticals Ltd</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -5209,237 +6106,140 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>27.85</v>
+        <v>24.15</v>
       </c>
       <c r="F6" t="n">
-        <v>34.76</v>
+        <v>23.2</v>
       </c>
       <c r="G6" t="n">
-        <v>29.28</v>
+        <v>15.44</v>
       </c>
       <c r="H6" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="I6" t="n">
+        <v>3106</v>
+      </c>
+      <c r="J6" t="n">
+        <v>30.59</v>
+      </c>
+      <c r="K6" t="n">
+        <v>6.93</v>
+      </c>
+      <c r="L6" t="n">
+        <v>30.39</v>
+      </c>
+      <c r="M6" t="n">
+        <v>9.93</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="O6" t="n">
+        <v>88.79000000000001</v>
+      </c>
+      <c r="P6" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q6" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="R6" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="S6" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I6" t="n">
-        <v>18742</v>
-      </c>
-      <c r="J6" t="n">
-        <v>10.08</v>
-      </c>
-      <c r="K6" t="n">
-        <v>7.95</v>
-      </c>
-      <c r="L6" t="n">
-        <v>9.859999999999999</v>
-      </c>
-      <c r="M6" t="n">
-        <v>362.96</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0.77</v>
-      </c>
-      <c r="O6" t="n">
-        <v>79.56</v>
-      </c>
-      <c r="P6" t="n">
-        <v>71.42857142857143</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>71.42857142857143</v>
-      </c>
-      <c r="R6" t="n">
-        <v>100</v>
-      </c>
-      <c r="S6" t="n">
-        <v>85.71428571428572</v>
-      </c>
-      <c r="T6" t="n">
-        <v>100</v>
-      </c>
-      <c r="U6" t="n">
-        <v>33.33333333333333</v>
-      </c>
-      <c r="V6" t="n">
-        <v>42.85714285714285</v>
-      </c>
-      <c r="W6" t="n">
-        <v>50</v>
-      </c>
-      <c r="X6" t="n">
-        <v>100</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>35.71428571428572</v>
+      <c r="T6" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="U6" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="V6" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="W6" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="X6" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y6" s="2" t="n">
+        <v>80</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>FMCG</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>NESTLEIND</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Mar 2024</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>117.75</v>
-      </c>
-      <c r="F7" t="n">
-        <v>185.43</v>
-      </c>
-      <c r="G7" t="n">
-        <v>16.12</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I7" t="n">
-        <v>2938</v>
-      </c>
-      <c r="J7" t="n">
-        <v>14.85</v>
-      </c>
-      <c r="K7" t="n">
-        <v>14.55</v>
-      </c>
-      <c r="L7" t="n">
-        <v>15.44</v>
-      </c>
-      <c r="M7" t="n">
-        <v>41.19</v>
-      </c>
-      <c r="N7" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="O7" t="n">
-        <v>84.19</v>
-      </c>
-      <c r="P7" t="n">
-        <v>100</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>100</v>
-      </c>
-      <c r="R7" t="n">
-        <v>71.42857142857143</v>
-      </c>
-      <c r="S7" t="n">
-        <v>57.14285714285715</v>
-      </c>
-      <c r="T7" t="n">
-        <v>57.14285714285714</v>
-      </c>
-      <c r="U7" t="n">
-        <v>83.33333333333334</v>
-      </c>
-      <c r="V7" t="n">
-        <v>85.71428571428571</v>
-      </c>
-      <c r="W7" t="n">
-        <v>100</v>
-      </c>
-      <c r="X7" t="n">
-        <v>71.42857142857143</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>FMCG</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>TATACONSUM</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Mar 2024</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>7.57</v>
-      </c>
-      <c r="F8" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="G8" t="n">
-        <v>7.99</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="I8" t="n">
-        <v>26</v>
-      </c>
-      <c r="J8" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="K8" t="n">
-        <v>15.96</v>
-      </c>
-      <c r="L8" t="n">
-        <v>14.87</v>
-      </c>
-      <c r="M8" t="n">
-        <v>25.32</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="O8" t="n">
-        <v>64.12</v>
-      </c>
-      <c r="P8" t="n">
-        <v>28.57142857142857</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>14.28571428571428</v>
-      </c>
-      <c r="R8" t="n">
-        <v>28.57142857142857</v>
-      </c>
-      <c r="S8" t="n">
-        <v>28.57142857142857</v>
-      </c>
-      <c r="T8" t="n">
-        <v>28.57142857142857</v>
-      </c>
-      <c r="U8" t="n">
-        <v>100</v>
-      </c>
-      <c r="V8" t="n">
-        <v>100</v>
-      </c>
-      <c r="W8" t="n">
-        <v>83.33333333333334</v>
-      </c>
-      <c r="X8" t="n">
-        <v>57.14285714285714</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>14.28571428571428</v>
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Median</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n"/>
+      <c r="C7" s="6" t="n"/>
+      <c r="D7" s="6" t="n"/>
+      <c r="E7" s="6" t="n">
+        <v>15.55</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>19.82</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>1152</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>23.39</v>
+      </c>
+      <c r="K7" s="6" t="n">
+        <v>9.66</v>
+      </c>
+      <c r="L7" s="6" t="n">
+        <v>23.84</v>
+      </c>
+      <c r="M7" s="6" t="n">
+        <v>51.71</v>
+      </c>
+      <c r="N7" s="6" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="O7" s="6" t="n">
+        <v>77.73</v>
+      </c>
+      <c r="P7" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="Q7" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="R7" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="S7" s="6" t="n">
+        <v>40</v>
+      </c>
+      <c r="T7" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="U7" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="V7" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="W7" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="X7" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="Y7" s="6" t="n">
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -5453,131 +6253,158 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y6"/>
+  <dimension ref="A1:Y9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="38" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="17" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="19" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="20" customWidth="1" min="13" max="13"/>
+    <col width="17" customWidth="1" min="14" max="14"/>
+    <col width="26" customWidth="1" min="15" max="15"/>
+    <col width="34" customWidth="1" min="16" max="16"/>
+    <col width="29" customWidth="1" min="17" max="17"/>
+    <col width="35" customWidth="1" min="18" max="18"/>
+    <col width="28" customWidth="1" min="19" max="19"/>
+    <col width="31" customWidth="1" min="20" max="20"/>
+    <col width="26" customWidth="1" min="21" max="21"/>
+    <col width="30" customWidth="1" min="22" max="22"/>
+    <col width="26" customWidth="1" min="23" max="23"/>
+    <col width="31" customWidth="1" min="24" max="24"/>
+    <col width="28" customWidth="1" min="25" max="25"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>peer_group_name</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>company_id</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>is_benchmark</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>year</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>return_on_equity_pct</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>roce_percentage</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>net_profit_margin_pct</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>debt_to_equity</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>free_cash_flow_cr</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>pat_cagr_5yr</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>revenue_cagr_5yr</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>eps_cagr_5yr</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>interest_coverage</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>asset_turnover</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>composite_quality_score</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>return_on_equity_pct_percentile</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>roce_percentage_percentile</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>net_profit_margin_pct_percentile</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>debt_to_equity_percentile</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>free_cash_flow_cr_percentile</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>pat_cagr_5yr_percentile</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>revenue_cagr_5yr_percentile</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>eps_cagr_5yr_percentile</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>interest_coverage_percentile</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>asset_turnover_percentile</t>
         </is>
@@ -5586,12 +6413,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>ADANIGREEN</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>CIPLA</t>
+          <t>Adani Green Energy Ltd</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -5605,78 +6432,70 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>15.55</v>
+        <v>12.81</v>
       </c>
       <c r="F2" t="n">
-        <v>22.8</v>
+        <v>96.5</v>
       </c>
       <c r="G2" t="n">
-        <v>16.12</v>
+        <v>13.67</v>
       </c>
       <c r="H2" t="n">
-        <v>0.02</v>
+        <v>6.6</v>
       </c>
       <c r="I2" t="n">
-        <v>1152</v>
-      </c>
-      <c r="J2" t="n">
-        <v>22.73</v>
-      </c>
+        <v>-13347</v>
+      </c>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="n">
-        <v>9.51</v>
-      </c>
-      <c r="L2" t="n">
-        <v>21.83</v>
-      </c>
+        <v>34.98</v>
+      </c>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
-        <v>35.34</v>
+        <v>1.71</v>
       </c>
       <c r="N2" t="n">
-        <v>0.79</v>
+        <v>0.1</v>
       </c>
       <c r="O2" t="n">
-        <v>75.34</v>
-      </c>
-      <c r="P2" t="n">
-        <v>60</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>60</v>
-      </c>
-      <c r="R2" t="n">
-        <v>40</v>
-      </c>
-      <c r="S2" t="n">
-        <v>60</v>
-      </c>
-      <c r="T2" t="n">
-        <v>60</v>
-      </c>
-      <c r="U2" t="n">
-        <v>40</v>
-      </c>
-      <c r="V2" t="n">
-        <v>40</v>
-      </c>
-      <c r="W2" t="n">
-        <v>40</v>
-      </c>
-      <c r="X2" t="n">
-        <v>40</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>100</v>
+        <v>59.67</v>
+      </c>
+      <c r="P2" s="3" t="n">
+        <v>42.85714285714285</v>
+      </c>
+      <c r="Q2" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>42.85714285714285</v>
+      </c>
+      <c r="S2" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" s="4" t="n">
+        <v>14.28571428571428</v>
+      </c>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" s="4" t="n">
+        <v>14.28571428571428</v>
+      </c>
+      <c r="Y2" s="4" t="n">
+        <v>21.42857142857143</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>ADANIPOWER</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>DIVISLAB</t>
+          <t>Adani Power Ltd</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -5690,78 +6509,70 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>11.79</v>
+        <v>48.28</v>
       </c>
       <c r="F3" t="n">
-        <v>16.5</v>
+        <v>32.2</v>
       </c>
       <c r="G3" t="n">
-        <v>20.4</v>
+        <v>41.37</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="I3" t="n">
-        <v>992</v>
-      </c>
-      <c r="J3" t="n">
-        <v>3.41</v>
-      </c>
+        <v>17651</v>
+      </c>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="n">
-        <v>9.66</v>
-      </c>
-      <c r="L3" t="n">
-        <v>3.3</v>
-      </c>
+        <v>16.09</v>
+      </c>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
-        <v>636.25</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="N3" t="n">
-        <v>0.51</v>
+        <v>0.55</v>
       </c>
       <c r="O3" t="n">
-        <v>68.5</v>
-      </c>
-      <c r="P3" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>20</v>
-      </c>
-      <c r="R3" t="n">
-        <v>100</v>
-      </c>
-      <c r="S3" t="n">
-        <v>80</v>
-      </c>
-      <c r="T3" t="n">
-        <v>40</v>
-      </c>
-      <c r="U3" t="n">
-        <v>20</v>
-      </c>
-      <c r="V3" t="n">
-        <v>60</v>
-      </c>
-      <c r="W3" t="n">
-        <v>20</v>
-      </c>
-      <c r="X3" t="n">
-        <v>100</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>20</v>
+        <v>88.79000000000001</v>
+      </c>
+      <c r="P3" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q3" s="2" t="n">
+        <v>85.71428571428571</v>
+      </c>
+      <c r="R3" s="2" t="n">
+        <v>85.71428571428571</v>
+      </c>
+      <c r="S3" s="2" t="n">
+        <v>85.71428571428572</v>
+      </c>
+      <c r="T3" s="2" t="n">
+        <v>85.71428571428571</v>
+      </c>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" s="2" t="n">
+        <v>85.71428571428571</v>
+      </c>
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" s="2" t="n">
+        <v>85.71428571428571</v>
+      </c>
+      <c r="Y3" s="2" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>JSWENERGY</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>DRREDDY</t>
+          <t>JSW Energy Ltd</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -5775,83 +6586,84 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>19.74</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>26.5</v>
+        <v>8.59</v>
       </c>
       <c r="G4" t="n">
-        <v>19.91</v>
+        <v>15.02</v>
       </c>
       <c r="H4" t="n">
-        <v>0.07000000000000001</v>
+        <v>1.52</v>
       </c>
       <c r="I4" t="n">
-        <v>509</v>
+        <v>-1963</v>
       </c>
       <c r="J4" t="n">
-        <v>23.39</v>
+        <v>20.32</v>
       </c>
       <c r="K4" t="n">
-        <v>12.64</v>
+        <v>4.68</v>
       </c>
       <c r="L4" t="n">
-        <v>23.84</v>
+        <v>20.11</v>
       </c>
       <c r="M4" t="n">
-        <v>51.71</v>
+        <v>2.85</v>
       </c>
       <c r="N4" t="n">
-        <v>0.72</v>
+        <v>0.2</v>
       </c>
       <c r="O4" t="n">
-        <v>77.73</v>
-      </c>
-      <c r="P4" t="n">
-        <v>80</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>100</v>
-      </c>
-      <c r="R4" t="n">
-        <v>80</v>
-      </c>
-      <c r="S4" t="n">
-        <v>20</v>
-      </c>
-      <c r="T4" t="n">
-        <v>20</v>
-      </c>
-      <c r="U4" t="n">
-        <v>60</v>
-      </c>
-      <c r="V4" t="n">
-        <v>100</v>
-      </c>
-      <c r="W4" t="n">
-        <v>60</v>
-      </c>
-      <c r="X4" t="n">
-        <v>60</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>60</v>
+        <v>66.79000000000001</v>
+      </c>
+      <c r="P4" s="4" t="n">
+        <v>14.28571428571428</v>
+      </c>
+      <c r="Q4" s="3" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>57.14285714285714</v>
+      </c>
+      <c r="S4" s="3" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="T4" s="3" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="U4" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="V4" s="3" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="W4" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="X4" s="3" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="Y4" s="3" t="n">
+        <v>57.14285714285714</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>NHPC</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SUNPHARMA</t>
+          <t xml:space="preserve">NHPC Ltd
+</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -5860,152 +6672,396 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>15.09</v>
+        <v>10.41</v>
       </c>
       <c r="F5" t="n">
-        <v>17.3</v>
+        <v>7.67</v>
       </c>
       <c r="G5" t="n">
-        <v>19.82</v>
+        <v>41.82</v>
       </c>
       <c r="H5" t="n">
-        <v>0.05</v>
+        <v>0.84</v>
       </c>
       <c r="I5" t="n">
-        <v>11372</v>
+        <v>970</v>
       </c>
       <c r="J5" t="n">
-        <v>24.54</v>
+        <v>7.27</v>
       </c>
       <c r="K5" t="n">
-        <v>10.78</v>
+        <v>1.4</v>
       </c>
       <c r="L5" t="n">
-        <v>29.46</v>
+        <v>5.92</v>
       </c>
       <c r="M5" t="n">
-        <v>58.33</v>
+        <v>11.24</v>
       </c>
       <c r="N5" t="n">
-        <v>0.57</v>
+        <v>0.1</v>
       </c>
       <c r="O5" t="n">
-        <v>85.44</v>
-      </c>
-      <c r="P5" t="n">
-        <v>40</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>40</v>
-      </c>
-      <c r="R5" t="n">
-        <v>60</v>
-      </c>
-      <c r="S5" t="n">
-        <v>40</v>
-      </c>
-      <c r="T5" t="n">
-        <v>100</v>
-      </c>
-      <c r="U5" t="n">
-        <v>80</v>
-      </c>
-      <c r="V5" t="n">
-        <v>80</v>
-      </c>
-      <c r="W5" t="n">
-        <v>80</v>
-      </c>
-      <c r="X5" t="n">
-        <v>80</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>40</v>
+        <v>67.84999999999999</v>
+      </c>
+      <c r="P5" s="3" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="Q5" s="4" t="n">
+        <v>14.28571428571428</v>
+      </c>
+      <c r="R5" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="S5" s="3" t="n">
+        <v>71.42857142857143</v>
+      </c>
+      <c r="T5" s="3" t="n">
+        <v>42.85714285714285</v>
+      </c>
+      <c r="U5" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="V5" s="4" t="n">
+        <v>14.28571428571428</v>
+      </c>
+      <c r="W5" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="X5" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="Y5" s="4" t="n">
+        <v>21.42857142857143</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Pharmaceuticals</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>TORNTPHARM</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>NTPC</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>NTPC Ltd</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>Mar 2024</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>13.27</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>10.58</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>11.95</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>8644</v>
+      </c>
+      <c r="J6" s="5" t="n">
+        <v>8.74</v>
+      </c>
+      <c r="K6" s="5" t="n">
+        <v>12.22</v>
+      </c>
+      <c r="L6" s="5" t="n">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="M6" s="5" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="N6" s="5" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="O6" s="5" t="n">
+        <v>68.90000000000001</v>
+      </c>
+      <c r="P6" s="3" t="n">
+        <v>71.42857142857143</v>
+      </c>
+      <c r="Q6" s="3" t="n">
+        <v>42.85714285714285</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="S6" s="3" t="n">
+        <v>42.85714285714286</v>
+      </c>
+      <c r="T6" s="3" t="n">
+        <v>71.42857142857143</v>
+      </c>
+      <c r="U6" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="V6" s="3" t="n">
+        <v>57.14285714285714</v>
+      </c>
+      <c r="W6" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="X6" s="3" t="n">
+        <v>64.28571428571429</v>
+      </c>
+      <c r="Y6" s="3" t="n">
+        <v>71.42857142857143</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>POWERGRID</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Power Grid Corporation of India Ltd</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>Mar 2024</t>
         </is>
       </c>
-      <c r="E6" t="n">
-        <v>24.15</v>
-      </c>
-      <c r="F6" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="G6" t="n">
-        <v>15.44</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="I6" t="n">
-        <v>3106</v>
-      </c>
-      <c r="J6" t="n">
-        <v>30.59</v>
-      </c>
-      <c r="K6" t="n">
-        <v>6.93</v>
-      </c>
-      <c r="L6" t="n">
-        <v>30.39</v>
-      </c>
-      <c r="M6" t="n">
-        <v>9.93</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="O6" t="n">
-        <v>88.79000000000001</v>
-      </c>
-      <c r="P6" t="n">
-        <v>100</v>
-      </c>
-      <c r="Q6" t="n">
+      <c r="E7" t="n">
+        <v>17.87</v>
+      </c>
+      <c r="F7" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="G7" t="n">
+        <v>33.97</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="I7" t="n">
+        <v>24176</v>
+      </c>
+      <c r="J7" t="n">
+        <v>9.19</v>
+      </c>
+      <c r="K7" t="n">
+        <v>5.51</v>
+      </c>
+      <c r="L7" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="M7" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="O7" t="n">
+        <v>75.15000000000001</v>
+      </c>
+      <c r="P7" s="2" t="n">
+        <v>85.71428571428571</v>
+      </c>
+      <c r="Q7" s="3" t="n">
+        <v>71.42857142857143</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>71.42857142857143</v>
+      </c>
+      <c r="S7" s="3" t="n">
+        <v>57.14285714285715</v>
+      </c>
+      <c r="T7" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="U7" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="V7" s="3" t="n">
+        <v>42.85714285714285</v>
+      </c>
+      <c r="W7" s="2" t="n">
         <v>80</v>
       </c>
-      <c r="R6" t="n">
-        <v>20</v>
-      </c>
-      <c r="S6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T6" t="n">
+      <c r="X7" s="3" t="n">
+        <v>64.28571428571429</v>
+      </c>
+      <c r="Y7" s="3" t="n">
+        <v>42.85714285714285</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>TATAPOWER</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tata Power Company Ltd
+</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Mar 2024</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>13.23</v>
+      </c>
+      <c r="F8" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>6.97</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="I8" t="n">
+        <v>3569</v>
+      </c>
+      <c r="J8" t="n">
+        <v>10.43</v>
+      </c>
+      <c r="K8" t="n">
+        <v>15.51</v>
+      </c>
+      <c r="L8" t="n">
+        <v>5.92</v>
+      </c>
+      <c r="M8" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="O8" t="n">
+        <v>65.54000000000001</v>
+      </c>
+      <c r="P8" s="3" t="n">
+        <v>57.14285714285714</v>
+      </c>
+      <c r="Q8" s="3" t="n">
+        <v>57.14285714285714</v>
+      </c>
+      <c r="R8" s="4" t="n">
+        <v>14.28571428571428</v>
+      </c>
+      <c r="S8" s="4" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="T8" s="3" t="n">
+        <v>57.14285714285714</v>
+      </c>
+      <c r="U8" s="2" t="n">
         <v>80</v>
       </c>
-      <c r="U6" t="n">
-        <v>100</v>
-      </c>
-      <c r="V6" t="n">
-        <v>20</v>
-      </c>
-      <c r="W6" t="n">
-        <v>100</v>
-      </c>
-      <c r="X6" t="n">
-        <v>20</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>80</v>
+      <c r="V8" s="3" t="n">
+        <v>71.42857142857143</v>
+      </c>
+      <c r="W8" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="X8" s="3" t="n">
+        <v>42.85714285714285</v>
+      </c>
+      <c r="Y8" s="2" t="n">
+        <v>85.71428571428571</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>Median</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="n"/>
+      <c r="C9" s="6" t="n"/>
+      <c r="D9" s="6" t="n"/>
+      <c r="E9" s="6" t="n">
+        <v>13.23</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>15.02</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>3569</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>9.19</v>
+      </c>
+      <c r="K9" s="6" t="n">
+        <v>12.22</v>
+      </c>
+      <c r="L9" s="6" t="n">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="M9" s="6" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="N9" s="6" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="O9" s="6" t="n">
+        <v>67.84999999999999</v>
+      </c>
+      <c r="P9" s="6" t="n">
+        <v>57.14</v>
+      </c>
+      <c r="Q9" s="6" t="n">
+        <v>57.14</v>
+      </c>
+      <c r="R9" s="6" t="n">
+        <v>57.14</v>
+      </c>
+      <c r="S9" s="6" t="n">
+        <v>42.86</v>
+      </c>
+      <c r="T9" s="6" t="n">
+        <v>57.14</v>
+      </c>
+      <c r="U9" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="V9" s="6" t="n">
+        <v>57.14</v>
+      </c>
+      <c r="W9" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="X9" s="6" t="n">
+        <v>64.29000000000001</v>
+      </c>
+      <c r="Y9" s="6" t="n">
+        <v>57.14</v>
       </c>
     </row>
   </sheetData>
@@ -6019,131 +7075,158 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y6"/>
+  <dimension ref="A1:Y7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="27" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="17" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="19" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="20" customWidth="1" min="13" max="13"/>
+    <col width="17" customWidth="1" min="14" max="14"/>
+    <col width="26" customWidth="1" min="15" max="15"/>
+    <col width="34" customWidth="1" min="16" max="16"/>
+    <col width="29" customWidth="1" min="17" max="17"/>
+    <col width="35" customWidth="1" min="18" max="18"/>
+    <col width="28" customWidth="1" min="19" max="19"/>
+    <col width="31" customWidth="1" min="20" max="20"/>
+    <col width="26" customWidth="1" min="21" max="21"/>
+    <col width="30" customWidth="1" min="22" max="22"/>
+    <col width="26" customWidth="1" min="23" max="23"/>
+    <col width="31" customWidth="1" min="24" max="24"/>
+    <col width="28" customWidth="1" min="25" max="25"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>peer_group_name</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>company_id</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>is_benchmark</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>year</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>return_on_equity_pct</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>roce_percentage</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>net_profit_margin_pct</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>debt_to_equity</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>free_cash_flow_cr</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>pat_cagr_5yr</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>revenue_cagr_5yr</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>eps_cagr_5yr</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>interest_coverage</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>asset_turnover</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>composite_quality_score</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>return_on_equity_pct_percentile</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>roce_percentage_percentile</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>net_profit_margin_pct_percentile</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>debt_to_equity_percentile</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>free_cash_flow_cr_percentile</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>pat_cagr_5yr_percentile</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>revenue_cagr_5yr_percentile</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>eps_cagr_5yr_percentile</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>interest_coverage_percentile</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>asset_turnover_percentile</t>
         </is>
@@ -6152,12 +7235,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>IT Services</t>
+          <t>AXISBANK</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>HCLTECH</t>
+          <t>Axis Bank Ltd</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -6171,163 +7254,163 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>23.01</v>
+        <v>15.83</v>
       </c>
       <c r="F2" t="n">
-        <v>29.6</v>
+        <v>7.06</v>
       </c>
       <c r="G2" t="n">
-        <v>14.29</v>
+        <v>22.73</v>
       </c>
       <c r="H2" t="n">
-        <v>0.08</v>
+        <v>8.25</v>
       </c>
       <c r="I2" t="n">
-        <v>15840</v>
+        <v>-14556</v>
       </c>
       <c r="J2" t="n">
-        <v>9.19</v>
+        <v>39.67</v>
       </c>
       <c r="K2" t="n">
-        <v>12.71</v>
+        <v>14.74</v>
       </c>
       <c r="L2" t="n">
-        <v>9.41</v>
+        <v>35.1</v>
       </c>
       <c r="M2" t="n">
-        <v>46.46</v>
+        <v>1.69</v>
       </c>
       <c r="N2" t="n">
-        <v>1.11</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="O2" t="n">
-        <v>80.11</v>
-      </c>
-      <c r="P2" t="n">
-        <v>60</v>
-      </c>
-      <c r="Q2" t="n">
+        <v>60.76</v>
+      </c>
+      <c r="P2" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="Q2" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="R2" s="3" t="n">
         <v>40</v>
       </c>
-      <c r="R2" t="n">
-        <v>60</v>
-      </c>
-      <c r="S2" t="n">
+      <c r="S2" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="U2" s="2" t="n">
         <v>80</v>
       </c>
-      <c r="T2" t="n">
-        <v>60</v>
-      </c>
-      <c r="U2" t="n">
-        <v>60</v>
-      </c>
-      <c r="V2" t="n">
-        <v>60</v>
-      </c>
-      <c r="W2" t="n">
-        <v>60</v>
-      </c>
-      <c r="X2" t="n">
-        <v>60</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>20</v>
+      <c r="V2" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="W2" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="X2" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="Y2" s="3" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>IT Services</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>INFY</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>HDFCBANK</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>HDFC Bank Ltd</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
         <is>
           <t>Mar 2024</t>
         </is>
       </c>
-      <c r="E3" t="n">
-        <v>29.79</v>
-      </c>
-      <c r="F3" t="n">
+      <c r="E3" s="5" t="n">
+        <v>14.34</v>
+      </c>
+      <c r="F3" s="5" t="n">
+        <v>7.67</v>
+      </c>
+      <c r="G3" s="5" t="n">
+        <v>23.07</v>
+      </c>
+      <c r="H3" s="5" t="n">
+        <v>6.81</v>
+      </c>
+      <c r="I3" s="5" t="n">
+        <v>35669</v>
+      </c>
+      <c r="J3" s="5" t="n">
+        <v>23.87</v>
+      </c>
+      <c r="K3" s="5" t="n">
+        <v>21.95</v>
+      </c>
+      <c r="L3" s="5" t="n">
+        <v>15.42</v>
+      </c>
+      <c r="M3" s="5" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="N3" s="5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="O3" s="5" t="n">
+        <v>49.05</v>
+      </c>
+      <c r="P3" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="Q3" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="S3" s="3" t="n">
         <v>40</v>
       </c>
-      <c r="G3" t="n">
-        <v>17.08</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="I3" t="n">
-        <v>20117</v>
-      </c>
-      <c r="J3" t="n">
-        <v>11.24</v>
-      </c>
-      <c r="K3" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="L3" t="n">
-        <v>12.47</v>
-      </c>
-      <c r="M3" t="n">
-        <v>87.52</v>
-      </c>
-      <c r="N3" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="O3" t="n">
-        <v>83.59</v>
-      </c>
-      <c r="P3" t="n">
-        <v>80</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>80</v>
-      </c>
-      <c r="R3" t="n">
-        <v>80</v>
-      </c>
-      <c r="S3" t="n">
+      <c r="T3" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="U3" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="V3" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="W3" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="X3" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="Y3" s="3" t="n">
         <v>50</v>
-      </c>
-      <c r="T3" t="n">
-        <v>80</v>
-      </c>
-      <c r="U3" t="n">
-        <v>80</v>
-      </c>
-      <c r="V3" t="n">
-        <v>80</v>
-      </c>
-      <c r="W3" t="n">
-        <v>100</v>
-      </c>
-      <c r="X3" t="n">
-        <v>100</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>40</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>IT Services</t>
+          <t>ICICIBANK</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>LTIM</t>
+          <t>ICICI Bank Ltd</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -6341,83 +7424,83 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>22.9</v>
+        <v>17.99</v>
       </c>
       <c r="F4" t="n">
-        <v>34.1</v>
+        <v>7.6</v>
       </c>
       <c r="G4" t="n">
-        <v>12.91</v>
+        <v>28.89</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1</v>
+        <v>6.45</v>
       </c>
       <c r="I4" t="n">
-        <v>1752</v>
+        <v>12547</v>
       </c>
       <c r="J4" t="n">
-        <v>24.78</v>
+        <v>51.95</v>
       </c>
       <c r="K4" t="n">
-        <v>30.33</v>
+        <v>17.25</v>
       </c>
       <c r="L4" t="n">
-        <v>12.24</v>
+        <v>55.18</v>
       </c>
       <c r="M4" t="n">
-        <v>31.93</v>
+        <v>1.3</v>
       </c>
       <c r="N4" t="n">
-        <v>1.29</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="O4" t="n">
-        <v>72.55</v>
-      </c>
-      <c r="P4" t="n">
+        <v>63.6</v>
+      </c>
+      <c r="P4" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q4" s="3" t="n">
         <v>40</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="S4" s="3" t="n">
         <v>60</v>
       </c>
-      <c r="R4" t="n">
+      <c r="T4" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="U4" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="V4" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="W4" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="X4" s="3" t="n">
         <v>40</v>
       </c>
-      <c r="S4" t="n">
-        <v>10</v>
-      </c>
-      <c r="T4" t="n">
-        <v>20</v>
-      </c>
-      <c r="U4" t="n">
-        <v>100</v>
-      </c>
-      <c r="V4" t="n">
-        <v>100</v>
-      </c>
-      <c r="W4" t="n">
-        <v>80</v>
-      </c>
-      <c r="X4" t="n">
-        <v>40</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>80</v>
+      <c r="Y4" s="3" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>IT Services</t>
+          <t>INDUSINDBK</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>TCS</t>
+          <t>IndusInd Bank Ltd</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -6426,78 +7509,79 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>50.94</v>
+        <v>14.25</v>
       </c>
       <c r="F5" t="n">
-        <v>64.3</v>
+        <v>7.93</v>
       </c>
       <c r="G5" t="n">
-        <v>19.14</v>
+        <v>19.56</v>
       </c>
       <c r="H5" t="n">
+        <v>6.89</v>
+      </c>
+      <c r="I5" t="n">
+        <v>-17468</v>
+      </c>
+      <c r="J5" t="n">
+        <v>22.08</v>
+      </c>
+      <c r="K5" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="L5" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="N5" t="n">
         <v>0.09</v>
       </c>
-      <c r="I5" t="n">
-        <v>50429</v>
-      </c>
-      <c r="J5" t="n">
-        <v>7.87</v>
-      </c>
-      <c r="K5" t="n">
-        <v>10.46</v>
-      </c>
-      <c r="L5" t="n">
-        <v>8.619999999999999</v>
-      </c>
-      <c r="M5" t="n">
-        <v>87.09999999999999</v>
-      </c>
-      <c r="N5" t="n">
-        <v>1.66</v>
-      </c>
       <c r="O5" t="n">
-        <v>85.89</v>
-      </c>
-      <c r="P5" t="n">
-        <v>100</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>100</v>
-      </c>
-      <c r="R5" t="n">
-        <v>100</v>
-      </c>
-      <c r="S5" t="n">
-        <v>50</v>
-      </c>
-      <c r="T5" t="n">
-        <v>100</v>
-      </c>
-      <c r="U5" t="n">
+        <v>52.45</v>
+      </c>
+      <c r="P5" s="3" t="n">
         <v>40</v>
       </c>
-      <c r="V5" t="n">
+      <c r="Q5" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="R5" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="S5" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="T5" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="U5" s="3" t="n">
         <v>40</v>
       </c>
-      <c r="W5" t="n">
+      <c r="V5" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="W5" s="3" t="n">
         <v>40</v>
       </c>
-      <c r="X5" t="n">
-        <v>80</v>
-      </c>
-      <c r="Y5" t="n">
+      <c r="X5" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="Y5" s="2" t="n">
         <v>100</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>IT Services</t>
+          <t>KOTAKBANK</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>TECHM</t>
+          <t xml:space="preserve">Kotak Mahindra Bank Ltd
+</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -6511,67 +7595,140 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>8.99</v>
+        <v>14.01</v>
       </c>
       <c r="F6" t="n">
-        <v>11.9</v>
+        <v>7.86</v>
       </c>
       <c r="G6" t="n">
-        <v>4.61</v>
+        <v>32.39</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1</v>
+        <v>4</v>
       </c>
       <c r="I6" t="n">
-        <v>5058</v>
+        <v>6766</v>
       </c>
       <c r="J6" t="n">
-        <v>-10.99</v>
+        <v>20.38</v>
       </c>
       <c r="K6" t="n">
-        <v>8.4</v>
+        <v>13.52</v>
       </c>
       <c r="L6" t="n">
-        <v>-11.42</v>
+        <v>19.34</v>
       </c>
       <c r="M6" t="n">
-        <v>13.86</v>
+        <v>1.24</v>
       </c>
       <c r="N6" t="n">
-        <v>1.21</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="O6" t="n">
-        <v>64.93000000000001</v>
-      </c>
-      <c r="P6" t="n">
+        <v>65.58</v>
+      </c>
+      <c r="P6" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="Q6" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="R6" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="S6" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="T6" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="U6" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="R6" t="n">
+      <c r="V6" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="S6" t="n">
-        <v>10</v>
-      </c>
-      <c r="T6" t="n">
+      <c r="W6" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="X6" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y6" s="3" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Median</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n"/>
+      <c r="C7" s="6" t="n"/>
+      <c r="D7" s="6" t="n"/>
+      <c r="E7" s="6" t="n">
+        <v>14.34</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>7.67</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>23.07</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>6.81</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>6766</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>23.87</v>
+      </c>
+      <c r="K7" s="6" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="L7" s="6" t="n">
+        <v>19.34</v>
+      </c>
+      <c r="M7" s="6" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="N7" s="6" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="O7" s="6" t="n">
+        <v>60.76</v>
+      </c>
+      <c r="P7" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="Q7" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="R7" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="S7" s="6" t="n">
         <v>40</v>
       </c>
-      <c r="U6" t="n">
-        <v>20</v>
-      </c>
-      <c r="V6" t="n">
-        <v>20</v>
-      </c>
-      <c r="W6" t="n">
-        <v>20</v>
-      </c>
-      <c r="X6" t="n">
-        <v>20</v>
-      </c>
-      <c r="Y6" t="n">
+      <c r="T7" s="6" t="n">
         <v>60</v>
+      </c>
+      <c r="U7" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="V7" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="W7" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="X7" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="Y7" s="6" t="n">
+        <v>50</v>
       </c>
     </row>
   </sheetData>
